--- a/02-data/02-gt-artifacts.xlsx
+++ b/02-data/02-gt-artifacts.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liuxiaoran/Downloads/icsa-2025-replication-package/02-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4274C53F-E777-B04D-9E5E-AC4BD20BBCC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3F85B6-DA82-0F43-9E19-AC58BC07B2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="axial_coding" sheetId="1" r:id="rId1"/>
-    <sheet name="selective_coding" sheetId="2" r:id="rId2"/>
-    <sheet name="final_RA" sheetId="3" r:id="rId3"/>
+    <sheet name="Axial coding" sheetId="1" r:id="rId1"/>
+    <sheet name="Selective coding" sheetId="2" r:id="rId2"/>
+    <sheet name="Final RA" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -24,13 +24,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="587">
   <si>
-    <t>components</t>
-  </si>
-  <si>
-    <t>layer</t>
-  </si>
-  <si>
-    <t>what does it do</t>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>What does it do</t>
   </si>
   <si>
     <t>Gymnasium</t>
@@ -3145,16 +3145,16 @@
     <t>examples/xxxxx/plotter.py, also can use tensorboarder</t>
   </si>
   <si>
-    <t>component group</t>
-  </si>
-  <si>
-    <t>component</t>
-  </si>
-  <si>
-    <t>interface</t>
-  </si>
-  <si>
-    <t>subcomponents</t>
+    <t>Component group</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>Subcomponents</t>
   </si>
   <si>
     <t>Experiment 
@@ -32404,7 +32404,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.1640625" bestFit="1" customWidth="1"/>
@@ -32904,7 +32904,7 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" customWidth="1"/>
     <col min="4" max="4" width="35.83203125" customWidth="1"/>

--- a/02-data/02-gt-artifacts.xlsx
+++ b/02-data/02-gt-artifacts.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liuxiaoran/Downloads/icsa-2025-replication-package/02-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3F85B6-DA82-0F43-9E19-AC58BC07B2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6931E5B-BE0D-8B4F-9327-83896AA10443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Axial coding" sheetId="1" r:id="rId1"/>
-    <sheet name="Selective coding" sheetId="2" r:id="rId2"/>
-    <sheet name="Final RA" sheetId="3" r:id="rId3"/>
+    <sheet name="axial-coding" sheetId="1" r:id="rId1"/>
+    <sheet name="selective-coding" sheetId="2" r:id="rId2"/>
+    <sheet name="final-RA" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -165,6 +165,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: Env</t>
@@ -189,6 +190,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: baseEnv</t>
@@ -265,6 +267,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> for RL environment, NO FILES</t>
@@ -361,6 +364,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -740,6 +744,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -759,6 +764,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, 
@@ -779,6 +785,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -930,6 +937,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -949,6 +957,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>, 
@@ -1111,6 +1120,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Basically:
@@ -1934,6 +1944,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>tianshou/highlevel/config.py
@@ -2275,6 +2286,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: 
@@ -2898,6 +2910,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -2919,6 +2932,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> class Logger
@@ -3489,6 +3503,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3527,6 +3542,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3551,6 +3567,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3579,6 +3596,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (example)
@@ -3602,6 +3620,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3641,6 +3660,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3666,6 +3686,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">You </t>
@@ -3684,6 +3705,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>. An Algorithm typically holds a neural network for computing actions, called policy, the RL environment that you want to optimize against, a loss function, an optimizer, and some code describing the algorithm’s execution logic, like determining when to collect samples, when to update your model, etc..</t>
@@ -3705,6 +3727,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3731,6 +3754,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3752,6 +3776,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3787,6 +3812,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3814,6 +3840,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3837,6 +3864,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3864,6 +3892,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3888,6 +3917,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">create env, agent, checkpoint, logging
@@ -3919,6 +3949,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3945,6 +3976,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3985,6 +4017,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>rl_zoo3/hyperparams_opt.py
@@ -4015,6 +4048,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4050,6 +4084,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4085,6 +4120,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4108,6 +4144,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4136,6 +4173,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4164,6 +4202,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (example)
@@ -4191,6 +4230,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4213,6 +4253,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4238,6 +4279,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">You </t>
@@ -4256,6 +4298,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. An Algorithm typically holds a neural network for computing actions, called policy, the RL environment that you want to optimize against, a loss function, an optimizer, and some code describing the algorithm’s execution logic, like determining when to collect samples, when to update your model, etc..
@@ -4278,6 +4321,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -4305,6 +4349,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4340,6 +4385,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4377,6 +4423,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4400,6 +4447,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4426,6 +4474,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4467,6 +4516,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4494,6 +4544,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4529,6 +4580,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4550,6 +4602,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4583,6 +4636,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -4605,6 +4659,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4641,6 +4696,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4684,6 +4740,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4705,6 +4762,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4736,6 +4794,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4772,6 +4831,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">def _run_train_phase(self, statistics):
@@ -4796,6 +4856,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4823,6 +4884,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4846,6 +4908,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> with the configuration given at construction.
@@ -4869,6 +4932,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4890,6 +4954,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4917,6 +4982,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4944,6 +5010,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4969,6 +5036,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4989,6 +5057,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5013,6 +5082,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5034,6 +5104,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5070,6 +5141,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5100,6 +5172,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Config, lightweight configuration framework
@@ -5122,6 +5195,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5147,6 +5221,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5177,6 +5252,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5199,6 +5275,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5221,6 +5298,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5243,6 +5321,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5266,6 +5345,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5299,6 +5379,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5320,6 +5401,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5344,6 +5426,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5391,6 +5474,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5420,6 +5504,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5441,6 +5526,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>):
@@ -5487,6 +5573,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5519,6 +5606,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">)  
@@ -5539,6 +5627,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5570,6 +5659,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5592,6 +5682,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5633,6 +5724,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The first of these is Anakin, which can be used when environments are written in JAX. This enables end-to-end JIT compilation of the full MARL training loop for fast experiment run times on hardware accelerators. The second is Sebulba, which can be used when environments are not written in JAX. Sebulba is particularly useful when running RL experiments where a hardware accelerator can interact with many CPU cores at a time.</t>
@@ -5654,6 +5746,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5675,6 +5768,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5702,6 +5796,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5731,6 +5826,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5757,6 +5853,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5777,6 +5874,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5798,6 +5896,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5826,6 +5925,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5851,6 +5951,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5881,6 +5982,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5914,6 +6016,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5937,6 +6040,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5958,6 +6062,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5983,6 +6088,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6007,6 +6113,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6037,6 +6144,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -6059,6 +6167,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6081,6 +6190,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6101,6 +6211,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6127,6 +6238,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6151,6 +6263,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6171,6 +6284,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6198,6 +6312,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6223,6 +6338,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6243,6 +6359,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6267,6 +6384,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6288,6 +6406,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6319,6 +6438,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6345,6 +6465,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6368,6 +6489,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6392,6 +6514,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6420,6 +6543,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -6442,6 +6566,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6466,6 +6591,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6494,6 +6620,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6514,6 +6641,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6538,6 +6666,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6567,6 +6696,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6607,6 +6737,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6631,6 +6762,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6652,6 +6784,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6677,6 +6810,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6705,6 +6839,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6734,6 +6869,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6760,6 +6896,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6780,6 +6917,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6804,6 +6942,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6831,6 +6970,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6904,6 +7044,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6945,6 +7086,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -6977,6 +7119,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7000,6 +7143,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7028,6 +7172,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7050,6 +7195,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7077,6 +7223,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -7105,6 +7252,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>ml-agents-envs/mlagents_envs/environment.py</t>
@@ -7126,6 +7274,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7149,6 +7298,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7172,6 +7322,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7192,6 +7343,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7225,6 +7377,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7252,6 +7405,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7274,6 +7428,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7298,6 +7453,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7320,6 +7476,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7354,6 +7511,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7385,6 +7543,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -7421,6 +7580,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7442,6 +7602,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7467,6 +7628,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7488,6 +7650,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7508,6 +7671,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: The action manager that processes the raw actions sent to the environment and converts them to low-level commands that are sent to the simulation. It can be configured to accept raw actions at different levels of abstraction. For example, in case of a robotic arm, the raw actions can be joint torques, joint positions, or end-effector poses. Similarly for a mobile base, it can be  the joint torques, or the desired velocity of the floating base.
@@ -7528,6 +7692,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7548,6 +7713,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -7569,6 +7735,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7588,6 +7755,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -7610,6 +7778,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -7639,6 +7808,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Environment
@@ -7663,6 +7833,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7689,6 +7860,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7719,6 +7891,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7740,6 +7913,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7769,6 +7943,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7796,6 +7971,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7818,6 +7994,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7851,6 +8028,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7873,6 +8051,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7896,6 +8075,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7919,6 +8099,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7943,6 +8124,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7970,6 +8152,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7999,6 +8182,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8024,6 +8208,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8053,6 +8238,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8079,6 +8265,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8104,6 +8291,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8138,6 +8326,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8169,6 +8358,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8201,6 +8391,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8230,6 +8421,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8252,6 +8444,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8276,6 +8469,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8299,6 +8493,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8332,6 +8527,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -8365,6 +8561,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8392,6 +8589,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8420,6 +8618,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8450,6 +8649,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8487,6 +8687,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8536,6 +8737,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8574,6 +8776,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8594,6 +8797,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8627,6 +8831,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">examples/checkpointing/reload_experiment.py
@@ -8650,6 +8855,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8681,6 +8887,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8707,6 +8914,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8737,6 +8945,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8763,6 +8972,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8790,6 +9000,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8810,6 +9021,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> to your isaacgymenvs tasks:
@@ -8834,6 +9046,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8857,6 +9070,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8880,6 +9094,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8918,6 +9133,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8943,6 +9159,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8974,6 +9191,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9000,6 +9218,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9025,6 +9244,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9048,6 +9268,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9078,6 +9299,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">         
@@ -9102,6 +9324,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9129,6 +9352,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9151,6 +9375,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9173,6 +9398,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -9194,6 +9420,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9229,6 +9456,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -9252,6 +9480,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9276,6 +9505,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9307,6 +9537,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9333,6 +9564,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9356,6 +9588,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9377,6 +9610,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9400,6 +9634,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9421,6 +9656,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9442,6 +9678,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9464,6 +9701,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9489,6 +9727,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9510,6 +9749,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9532,6 +9772,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9555,6 +9796,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9581,6 +9823,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9617,6 +9860,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9639,6 +9883,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9665,6 +9910,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9690,6 +9936,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9717,6 +9964,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9739,6 +9987,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -9769,6 +10018,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9794,6 +10044,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9820,6 +10071,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9850,6 +10102,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9890,6 +10143,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9920,6 +10174,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9943,6 +10198,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9967,6 +10223,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9991,6 +10248,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10012,6 +10270,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10033,6 +10292,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10058,6 +10318,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -10093,6 +10354,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Logging &amp; Saving
@@ -10112,6 +10374,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. You can change the saved log location here:
@@ -10132,6 +10395,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -10153,6 +10417,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10180,6 +10445,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10207,6 +10473,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">(BaseLogger):
@@ -10241,6 +10508,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(BaseLogger):
@@ -10270,6 +10538,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10295,6 +10564,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10323,6 +10593,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10348,6 +10619,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10372,6 +10644,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10409,6 +10682,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10431,6 +10705,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10455,6 +10730,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">..)
@@ -10478,6 +10754,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10501,6 +10778,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10523,6 +10801,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10549,6 +10828,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10572,6 +10852,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10616,6 +10897,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10636,6 +10918,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -10656,6 +10939,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (
@@ -10688,6 +10972,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10710,6 +10995,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10729,6 +11015,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(
@@ -10783,6 +11070,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10805,6 +11093,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and log statistics.
@@ -32984,7 +33273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="28" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:20" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>316</v>
       </c>
@@ -33072,7 +33361,7 @@
       <c r="S3" s="17"/>
       <c r="T3" s="17"/>
     </row>
-    <row r="4" spans="1:20" ht="397" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" ht="306" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>320</v>
       </c>
@@ -33118,7 +33407,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="345" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:20" ht="280" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>320</v>
       </c>
@@ -33150,7 +33439,7 @@
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
     </row>
-    <row r="6" spans="1:20" ht="70" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:20" ht="56" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>320</v>
       </c>
@@ -33178,7 +33467,7 @@
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
-    <row r="7" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:20" ht="306" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>325</v>
       </c>
@@ -33268,7 +33557,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:20" ht="345" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>325</v>
       </c>
@@ -33348,7 +33637,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:20" ht="293" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>325</v>
       </c>
@@ -33382,7 +33671,7 @@
       <c r="S11" s="17"/>
       <c r="T11" s="17"/>
     </row>
-    <row r="12" spans="1:20" ht="224" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:20" ht="154" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>336</v>
       </c>
@@ -33426,7 +33715,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="306" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:20" ht="210" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>336</v>
       </c>
@@ -33472,7 +33761,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:20" ht="358" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>336</v>
       </c>
@@ -33650,7 +33939,7 @@
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
     </row>
-    <row r="18" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:20" ht="358" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>347</v>
       </c>
@@ -33784,7 +34073,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:20" ht="319" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>518</v>
       </c>

--- a/02-data/02-gt-artifacts.xlsx
+++ b/02-data/02-gt-artifacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liuxiaoran/Downloads/icsa-2025-replication-package/02-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6931E5B-BE0D-8B4F-9327-83896AA10443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E93309-EA34-0242-B9AA-62C812353C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="axial-coding" sheetId="1" r:id="rId1"/>
@@ -165,7 +165,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: Env</t>
@@ -190,7 +189,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: baseEnv</t>
@@ -267,7 +265,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> for RL environment, NO FILES</t>
@@ -364,7 +361,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -744,7 +740,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -764,7 +759,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, 
@@ -785,7 +779,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -937,7 +930,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -957,7 +949,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>, 
@@ -1120,7 +1111,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Basically:
@@ -1944,7 +1934,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>tianshou/highlevel/config.py
@@ -2286,7 +2275,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: 
@@ -2910,7 +2898,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -2932,7 +2919,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> class Logger
@@ -3503,7 +3489,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3542,7 +3527,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3567,7 +3551,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3596,7 +3579,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (example)
@@ -3620,7 +3602,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3660,7 +3641,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3686,7 +3666,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">You </t>
@@ -3705,7 +3684,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>. An Algorithm typically holds a neural network for computing actions, called policy, the RL environment that you want to optimize against, a loss function, an optimizer, and some code describing the algorithm’s execution logic, like determining when to collect samples, when to update your model, etc..</t>
@@ -3727,7 +3705,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3754,7 +3731,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3776,7 +3752,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3812,7 +3787,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3840,7 +3814,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3864,7 +3837,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3892,7 +3864,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3917,7 +3888,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">create env, agent, checkpoint, logging
@@ -3949,7 +3919,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -3976,7 +3945,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4017,7 +3985,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>rl_zoo3/hyperparams_opt.py
@@ -4048,7 +4015,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4084,7 +4050,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4120,7 +4085,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4144,7 +4108,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4173,7 +4136,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4202,7 +4164,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (example)
@@ -4230,7 +4191,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4253,7 +4213,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4279,7 +4238,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">You </t>
@@ -4298,7 +4256,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. An Algorithm typically holds a neural network for computing actions, called policy, the RL environment that you want to optimize against, a loss function, an optimizer, and some code describing the algorithm’s execution logic, like determining when to collect samples, when to update your model, etc..
@@ -4321,7 +4278,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -4349,7 +4305,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4385,7 +4340,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4423,7 +4377,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4447,7 +4400,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4474,7 +4426,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4516,7 +4467,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4544,7 +4494,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4580,7 +4529,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4602,7 +4550,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4636,7 +4583,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -4659,7 +4605,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4696,7 +4641,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4740,7 +4684,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4762,7 +4705,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4794,7 +4736,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4831,7 +4772,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">def _run_train_phase(self, statistics):
@@ -4856,7 +4796,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4884,7 +4823,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4908,7 +4846,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> with the configuration given at construction.
@@ -4932,7 +4869,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4954,7 +4890,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -4982,7 +4917,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5010,7 +4944,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5036,7 +4969,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5057,7 +4989,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5082,7 +5013,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5104,7 +5034,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5141,7 +5070,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5172,7 +5100,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Config, lightweight configuration framework
@@ -5195,7 +5122,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5221,7 +5147,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5252,7 +5177,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5275,7 +5199,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5298,7 +5221,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5321,7 +5243,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5345,7 +5266,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5379,7 +5299,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5401,7 +5320,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5426,7 +5344,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5474,7 +5391,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5504,7 +5420,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5526,7 +5441,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>):
@@ -5573,7 +5487,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5606,7 +5519,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">)  
@@ -5627,7 +5539,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5659,7 +5570,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5682,7 +5592,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5724,7 +5633,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The first of these is Anakin, which can be used when environments are written in JAX. This enables end-to-end JIT compilation of the full MARL training loop for fast experiment run times on hardware accelerators. The second is Sebulba, which can be used when environments are not written in JAX. Sebulba is particularly useful when running RL experiments where a hardware accelerator can interact with many CPU cores at a time.</t>
@@ -5746,7 +5654,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5768,7 +5675,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5796,7 +5702,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5826,7 +5731,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5853,7 +5757,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5874,7 +5777,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5896,7 +5798,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5925,7 +5826,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5951,7 +5851,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -5982,7 +5881,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6016,7 +5914,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6040,7 +5937,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6062,7 +5958,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6088,7 +5983,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6113,7 +6007,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6144,7 +6037,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -6167,7 +6059,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6190,7 +6081,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6211,7 +6101,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6238,7 +6127,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6263,7 +6151,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6284,7 +6171,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6312,7 +6198,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6338,7 +6223,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6359,7 +6243,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6384,7 +6267,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6406,7 +6288,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6438,7 +6319,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6465,7 +6345,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6489,7 +6368,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6514,7 +6392,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6543,7 +6420,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -6566,7 +6442,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6591,7 +6466,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6620,7 +6494,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6641,7 +6514,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6666,7 +6538,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6696,7 +6567,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6737,7 +6607,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6762,7 +6631,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6784,7 +6652,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6810,7 +6677,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6839,7 +6705,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6869,7 +6734,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6896,7 +6760,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6917,7 +6780,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6942,7 +6804,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -6970,7 +6831,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7044,7 +6904,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7086,7 +6945,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -7119,7 +6977,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7143,7 +7000,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7172,7 +7028,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7195,7 +7050,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7223,7 +7077,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -7252,7 +7105,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>ml-agents-envs/mlagents_envs/environment.py</t>
@@ -7274,7 +7126,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7298,7 +7149,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7322,7 +7172,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7343,7 +7192,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7377,7 +7225,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7405,7 +7252,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7428,7 +7274,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7453,7 +7298,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7476,7 +7320,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7511,7 +7354,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7543,7 +7385,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -7580,7 +7421,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -7602,7 +7442,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7628,7 +7467,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7650,7 +7488,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7671,7 +7508,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: The action manager that processes the raw actions sent to the environment and converts them to low-level commands that are sent to the simulation. It can be configured to accept raw actions at different levels of abstraction. For example, in case of a robotic arm, the raw actions can be joint torques, joint positions, or end-effector poses. Similarly for a mobile base, it can be  the joint torques, or the desired velocity of the floating base.
@@ -7692,7 +7528,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7713,7 +7548,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -7735,7 +7569,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7755,7 +7588,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -7778,7 +7610,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -7808,7 +7639,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Environment
@@ -7833,7 +7663,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7860,7 +7689,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7891,7 +7719,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7913,7 +7740,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7943,7 +7769,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7971,7 +7796,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -7994,7 +7818,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8028,7 +7851,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8051,7 +7873,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8075,7 +7896,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8099,7 +7919,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8124,7 +7943,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8152,7 +7970,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8182,7 +7999,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8208,7 +8024,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8238,7 +8053,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8265,7 +8079,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8291,7 +8104,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8326,7 +8138,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8358,7 +8169,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8391,7 +8201,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8421,7 +8230,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8444,7 +8252,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8469,7 +8276,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8493,7 +8299,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8527,7 +8332,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -8561,7 +8365,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8589,7 +8392,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8618,7 +8420,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8649,7 +8450,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8687,7 +8487,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8737,7 +8536,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8776,7 +8574,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8797,7 +8594,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8831,7 +8627,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">examples/checkpointing/reload_experiment.py
@@ -8855,7 +8650,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8887,7 +8681,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8914,7 +8707,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8945,7 +8737,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -8972,7 +8763,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9000,7 +8790,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9021,7 +8810,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> to your isaacgymenvs tasks:
@@ -9046,7 +8834,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9070,7 +8857,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9094,7 +8880,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9133,7 +8918,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9159,7 +8943,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9191,7 +8974,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9218,7 +9000,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9244,7 +9025,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9268,7 +9048,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9276,7 +9055,30 @@
 Run rendering without stepping through the physics.
 By convention, if mode is:
 human: Render to the current display and return nothing. Usually for human consumption.
-rgb_array: Return a numpy.ndarray with shape (x, y, 3), representing RGB values for an x-by-y pixel image, suitable for turning into a video.</t>
+rgb_array: Return a numpy.ndarray with shape (x, y, 3), representing RGB values for an x-by-y pixel image, suitable for turning into a video.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab_contrib/isaaclab_contrib/sensors/tacsl_sensor/visuotactile_render.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+class GelsightRender:
+    """Class to handle GelSight rendering using the Taxim example-based approach from :cite:t:`si2022taxim`.
+</t>
     </r>
   </si>
   <si>
@@ -9299,7 +9101,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">         
@@ -9324,7 +9125,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9352,7 +9152,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9375,7 +9174,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9398,7 +9196,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -9420,7 +9217,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9456,7 +9252,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -9480,7 +9275,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9505,7 +9299,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9537,7 +9330,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9564,7 +9356,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9588,7 +9379,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9610,7 +9400,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9634,7 +9423,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9656,7 +9444,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9678,7 +9465,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9701,7 +9487,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9727,7 +9512,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9749,7 +9533,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9772,7 +9555,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9796,7 +9578,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9823,7 +9604,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9860,7 +9640,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9883,7 +9662,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9910,7 +9688,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9936,7 +9713,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9964,7 +9740,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -9987,7 +9762,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -10018,7 +9792,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10044,7 +9817,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10071,7 +9843,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10102,7 +9873,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10143,7 +9913,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10174,7 +9943,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10198,7 +9966,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10223,7 +9990,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10248,7 +10014,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10270,7 +10035,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10292,7 +10056,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10318,7 +10081,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  
@@ -10354,7 +10116,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Logging &amp; Saving
@@ -10374,7 +10135,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. You can change the saved log location here:
@@ -10395,7 +10155,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -10417,7 +10176,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10445,7 +10203,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10473,7 +10230,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">(BaseLogger):
@@ -10508,7 +10264,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(BaseLogger):
@@ -10538,7 +10293,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10564,7 +10318,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10593,7 +10346,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10619,7 +10371,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10644,7 +10395,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10682,7 +10432,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10705,7 +10454,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10730,7 +10478,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">..)
@@ -10754,7 +10501,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10778,7 +10524,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10801,7 +10546,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10828,7 +10572,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10852,7 +10595,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10897,7 +10639,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10918,7 +10659,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -10939,7 +10679,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (
@@ -10972,7 +10711,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -10995,7 +10733,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -11015,7 +10752,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(
@@ -11070,7 +10806,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -11093,7 +10828,6 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and log statistics.
@@ -34117,10 +33851,10 @@
       <c r="C22" s="19" t="s">
         <v>536</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>537</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>538</v>
       </c>
       <c r="F22" s="19" t="s">
@@ -34135,7 +33869,7 @@
       <c r="I22" s="19" t="s">
         <v>542</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="18" t="s">
         <v>543</v>
       </c>
       <c r="K22" s="19" t="s">

--- a/02-data/02-gt-artifacts.xlsx
+++ b/02-data/02-gt-artifacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liuxiaoran/Downloads/icsa-2025-replication-package/02-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E93309-EA34-0242-B9AA-62C812353C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A8DA2A-FF84-8440-8B8F-04945F3F4F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="631">
   <si>
     <t>Components</t>
   </si>
@@ -3474,6 +3474,42 @@
     <t>use experiment logger results, generate metrics report, and plot</t>
   </si>
   <si>
+    <t>Development Team</t>
+  </si>
+  <si>
+    <t>Farama Foundation</t>
+  </si>
+  <si>
+    <t>Unity</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>Google DeepMind</t>
+  </si>
+  <si>
+    <t>Research Team at InstaDeep.</t>
+  </si>
+  <si>
+    <t>Antonin Raffin - German Aerospace Center (DLR)</t>
+  </si>
+  <si>
+    <t>RISELab at UCB, now company Anyscale.</t>
+  </si>
+  <si>
+    <t>small research team</t>
+  </si>
+  <si>
+    <t>Company: Meta</t>
+  </si>
+  <si>
+    <t>Company: Google</t>
+  </si>
+  <si>
+    <t>Research: Tsinghua University</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
@@ -8315,6 +8351,398 @@
   </si>
   <si>
     <t>Data Persistence</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Unity-Technologies/ml-agents/blob/develop/ml-agents/mlagents/trainers/policy/checkpoint_manager.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Unity-Technologies/ml-agents/blob/develop/ml-agents/mlagents/trainers/model_saver/model_saver.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Unity-Technologies/ml-agents/blob/develop/com.unity.ml-agents/Runtime/EnvironmentParameters.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacGymEnvs/blob/main/docs/domain_randomization.md?plain=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+We provide two interfaces to add 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>domain randomization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to your isaacgymenvs tasks:
+Adding domain randomization parameters to your task's YAML config
+Directly calling the apply_randomizations class method
+Provided your task inherits from our VecTask class, you have great flexibility in choosing when to randomize and what distributions to sample, and can even change the entire domain randomization dictionary at every call to apply_randomizations if you wish.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://isaac-sim.github.io/IsaacLab/main/source/tutorials/03_envs/create_direct_rl_env.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+In Isaac Lab, the domain randomization configuration 
+uses the configclass module to specify a configuration class 
+consisting of EventTermCfg variables.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab/isaaclab/managers/curriculum_manager.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+CurriculumManager:The curriculum manager updates various quantities of the environment subject to a training curriculum by calling a list of terms. 
+These help stabilize learning by progressively making the learning tasks harder as the agent improves.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Farama-Foundation/Arcade-Learning-Environment/blob/master/src/ale/ale_interface.hpp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+src/ale/ale_interface.hpp
+DifficultyVect getAvailableDifficulties() const;
+void setDifficulty(difficulty_t m);
+difficulty_t getDifficulty() 
+ModeVect getAvailableModes() const;
+void setMode(game_mode_t m);
+game_mode_t getMode()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/instadeepai/jumanji/blob/main/jumanji/training/loggers.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+class Logger(AbstractContextManager)
+write, close, upload_checkpoint(self) -&gt; None:
+        """Uploads a checkpoint when exiting the logger.
+_save_and_upload_checkpoint(self) -&gt; None:
+        """Grabs the `training_state` variable from within the context manager, pickles it and
+        saves it. This will break if the desired variable to checkpoint is not called
+        `training_state`.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/DLR-RM/stable-baselines3/blob/master/stable_baselines3/common/callbacks.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+stable_baselines3/common/callbacks.py
+class CheckpointCallback(BaseCallback):
+    """
+    Callback for saving a model every ``save_freq`` calls
+    to ``env.step()``.
+    By default, it only saves model checkpoints,
+    you need to pass ``save_replay_buffer=True``,
+    and ``save_vecnormalize=True`` to also save replay buffer checkpoints
+    and normalization statistics checkpoints.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/DLR-RM/rl-baselines3-zoo/blob/master/rl_zoo3/utils.py 	"def get_model_path(
+    exp_id: int,
+    folder: str,
+    algo: str,
+    env_name: EnvironmentName,
+    load_best: bool = False,
+    load_checkpoint: str | None = None,
+    load_last_checkpoint: bool = False,
+) -&gt; tuple[str, str, str]:
+    if exp_id == 0:
+        exp_id = get_latest_run_id(os.path.join(folder, algo), env_name)
+        print(f""Loading latest experiment, id={exp_id}"")"</t>
+  </si>
+  <si>
+    <t>https://github.com/ray-project/ray/blob/master/rllib/utils/checkpoints.py 
+rllib/utils/checkpoints.py
+class Checkpointable(abc.ABC):
+    """Abstract base class for a component of RLlib that can be checkpointed to disk</t>
+  </si>
+  <si>
+    <t>https://github.com/google-deepmind/acme/blob/master/acme/tf/savers.py 	"class Checkpointer:
+  """"""Convenience class for periodically checkpointing.
+ def save(self, force: bool = False) -&gt; bool:
+    """"""Save the checkpoint if it's the appropriate time, otherwise no-ops.
+ def restore(self):
+    """"""Restore from most recent checkpoint.""""""
+class CheckpointingRunner(core.Worker):
+  """"""Wrap an object and expose a run method which checkpoints periodically.
+"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UseRLlib (Ray), </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/ray-project/ray/blob/master/python/ray/tune/trainable/trainable_fn_utils.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/facebookresearch/BenchMARL/tree/main/examples/checkpointing	
+checkpointing folder, including reload and resume files</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/tree/develop/mava/utils</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">checkpointing.py
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utils have (i) checkpointing (ii) logger for logging and reporting (external)
+checkpointing: 
+class Checkpointer:
+    """Model checkpointer for saving and restoring the `learner_state`."""
+    def __init__(
+        self,
+        model_name: str,
+        metadata: Optional[Dict] = None,
+        rel_dir: str = "checkpoints",
+        checkpoint_uid: Optional[str] = None,
+        save_interval_steps: int = 1,
+        max_to_keep: Optional[int] = 1,
+        keep_period: Optional[int] = None,
+    ):
+        """Initialise the checkpointer tool</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/checkpointer.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+dopamine/discrete_domains/checkpointer.py
+"""A checkpointing mechanism for Dopamine agents.
+from absl import logging
+from dopamine.discrete_domains import atari_lib
+from dopamine.discrete_domains import checkpointer
+from dopamine.discrete_domains import iteration_statistics
+from dopamine.discrete_domains import logger
+class Checkpointer(object):
+  """Class for managing checkpoints for Dopamine agents."""</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">class Persistence(ABC):
+    @abstractmethod
+    def persist(self, event: PersistEvent, world: World) -&gt; None:
+        pass
+    @abstractmethod
+    def restore(self, event: RestoreEvent, world: World) -&gt; None:
+        pass
+class PersistenceGroup(Persistence):
+https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/persistence.py  </t>
   </si>
   <si>
     <r>
@@ -8896,6 +9324,362 @@
     <t>Monitoring &amp; Visualization</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Farama-Foundation/Gymnasium/tree/main/gymnasium/utils</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+utils module have: record &amp; save video
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Farama-Foundation/Gymnasium/blob/main/gymnasium/logger.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Logger
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/Farama-Foundation/Gymnasium/blob/main/gymnasium/wrappers/utils.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+wrapper utils</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/Farama-Foundation/PettingZoo/tree/master/pettingzoo/utils 	utils folder: logger, save, total reward...</t>
+  </si>
+  <si>
+    <t>"https://github.com/Unity-Technologies/ml-agents/blob/develop/ml-agents-envs/mlagents_envs/logging_util.py 
+https://github.com/Unity-Technologies/ml-agents/blob/develop/ml-agents/mlagents/trainers/stats.py "
+   """
+    Create a logger with the specified name. The logger will use the log level
+    specified by set_log_level()
+    """, 
+class StatsSummary(NamedTuple):
+class StatsWriter(abc.ABC):
+    """
+    A StatsWriter abstract class. A StatsWriter takes in a category, key, scalar value, and step
+    and writes it out by some method.
+    """</t>
+  </si>
+  <si>
+    <t>code are mainly in the vec_task, but not a standalone module. also, only use the logger/reporter by calling python libs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab/isaaclab/envs/manager_based_rl_env.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab_contrib/isaaclab_contrib/sensors/tacsl_sensor/visuotactile_render.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  
+class GelsightRender:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab/isaaclab/managers/recorder_manager.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/google-deepmind/dm_control/tree/main/dm_control/viewer	The dm_control.viewer library can be used to visualize and interact with a control environment. The following example shows how to launch the viewer with an environment from the Control Suite:	renderer, viewer, logger</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/google-deepmind/lab/tree/master/engine/code/renderercommon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/google-deepmind/lab/blob/master/game_scripts/common/log.lua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+multiple rendereer; logger files; and recording files</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/instadeepai/jumanji/blob/main/jumanji/env.py ;
+https://github.com/instadeepai/jumanji/blob/main/jumanji/viewer.py 
+https://github.com/instadeepai/jumanji/blob/main/jumanji/training/loggers.py </t>
+  </si>
+  <si>
+    <t>https://github.com/DLR-RM/stable-baselines3/tree/master/stable_baselines3/common	
+logger.py monitor.py save_util.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/DLR-RM/rl-baselines3-zoo/blob/master/rl_zoo3/record_training.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/DLR-RM/rl-baselines3-zoo/blob/master/rl_zoo3/record_video.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/DLR-RM/rl-baselines3-zoo/tree/master/rl_zoo3/plots</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/ray-project/ray/tree/master/rllib/utils
+have metrics for reporting, error for logging.</t>
+  </si>
+  <si>
+    <t>"https://github.com/google-deepmind/acme/tree/master/acme/utils/loggers
+https://github.com/google-deepmind/acme/blob/master/acme/wrappers/video.py
+utils/loggers
+wrappers/video.py</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use RLLib (Ray): </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/ray-project/ray/blob/master/python/ray/tune/progress_reporter.py</t>
+    </r>
+  </si>
+  <si>
+    <t>"class Logger:
+    def __init__(
+        self,
+        experiment_name: str,
+        folder_name: str,
+        experiment_config,
+        algorithm_name: str,
+        environment_name: str,
+        task_name: str,
+        model_name: str,
+        group_map: Dict[str, List[str]],
+        seed: int,
+        project_name: str,
+        wandb_extra_kwargs: Dict[str, Any],
+    ):"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/utils/logger.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+class MavaLogger:
+    def __init__(
+        self,
+        config: DictConfig,
+        custom_metrics_fn: Callable[[Metrics], Metrics] = winrate_custom_metric,
+    ) -&gt; None:
+        """The main logger for Mava systems.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">https://github.com/google/dopamine/tree/master/dopamine/utils 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Utils has bar_plotter, line_plotter, agent_visualizer, etc.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/logger.py 
+tianshou/highlevel/logger.py
+from tianshou.utils import BaseLogger, TensorboardLogger, WandbLogger
+"""A logger that relies on tensorboard SummaryWriter by default to visualize and log statistics.</t>
+  </si>
+  <si>
     <t>Renderer</t>
   </si>
   <si>
@@ -9167,7 +9951,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>https://github.com/Farama-Foundation/Arcade-Learning-Environment/blob/master/src/ale/python/env.py</t>
+      <t>https://github.com/Farama-Foundation/Arcade-Learning-Environment/blob/master/src/ale/common/ScreenSDL.hpp</t>
     </r>
     <r>
       <rPr>
@@ -9177,7 +9961,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 
-render()</t>
+A method called render() that displays frames</t>
     </r>
   </si>
   <si>
@@ -9745,34 +10529,6 @@
       <t xml:space="preserve"> 
 isaacgymenvs/tasks/amp/poselib/poselib/core/backend/logger.py  
 import logging
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://github.com/isaac-sim/IsaacGymEnvs/blob/main/isaacgymenvs/learning/common_agent.py</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-from tensorboardX import SummaryWriter
-self.eval_summary_dir = "./eval_summaries"
-# remove the old directory if it exists
-if os.path.exists(self.eval_summary_dir):
-import shutil
-shutil.rmtree(self.eval_summary_dir)
-self.eval_summaries = SummaryWriter(self.eval_summary_dir, flush_secs=3)
-The SummaryWriter class is your main entry to log data for consumption and visualization by TensorBoard. 
 </t>
     </r>
   </si>
@@ -10207,13 +10963,6 @@
       </rPr>
       <t xml:space="preserve"> 
 mava/utils/logger.py
-class MavaLogger:
-    def __init__(
-        self,
-        config: DictConfig,
-        custom_metrics_fn: Callable[[Metrics], Metrics] = winrate_custom_metric,
-    ) -&gt; None:
-        """The main logger for Mava systems.
 class </t>
     </r>
     <r>
@@ -10834,12 +11583,33 @@
 </t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://www.tensorflow.org/resources/libraries-extensions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -10928,6 +11698,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF474747"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
@@ -10956,6 +11732,27 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -11152,7 +11949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11194,33 +11991,53 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32608,7 +33425,7 @@
       <c r="AA8" s="16"/>
     </row>
     <row r="9" spans="1:27" ht="56" x14ac:dyDescent="0.15">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="33" t="s">
         <v>336</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -32626,7 +33443,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="28" x14ac:dyDescent="0.15">
-      <c r="A10" s="26"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="4" t="s">
         <v>340</v>
       </c>
@@ -32642,7 +33459,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="70" x14ac:dyDescent="0.15">
-      <c r="A11" s="26"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="4" t="s">
         <v>262</v>
       </c>
@@ -32658,7 +33475,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="56" x14ac:dyDescent="0.15">
-      <c r="A12" s="27"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="4" t="s">
         <v>345</v>
       </c>
@@ -32670,13 +33487,13 @@
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:27" ht="42" x14ac:dyDescent="0.15">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="33" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="33" t="s">
         <v>347</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="33" t="s">
         <v>348</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -32690,9 +33507,9 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="28" x14ac:dyDescent="0.15">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="4" t="s">
         <v>351</v>
       </c>
@@ -32704,9 +33521,9 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="28" x14ac:dyDescent="0.15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="4" t="s">
         <v>354</v>
       </c>
@@ -32718,9 +33535,9 @@
       </c>
     </row>
     <row r="16" spans="1:27" ht="42" x14ac:dyDescent="0.15">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="8" t="s">
         <v>142</v>
       </c>
@@ -32751,9 +33568,9 @@
       <c r="AA16" s="12"/>
     </row>
     <row r="17" spans="1:6" ht="56" x14ac:dyDescent="0.15">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
       <c r="D17" s="8" t="s">
         <v>117</v>
       </c>
@@ -32765,11 +33582,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="42" x14ac:dyDescent="0.15">
-      <c r="A18" s="26"/>
-      <c r="B18" s="25" t="s">
+      <c r="A18" s="34"/>
+      <c r="B18" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="33" t="s">
         <v>360</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -32783,9 +33600,9 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.15">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
       <c r="D19" s="4" t="s">
         <v>364</v>
       </c>
@@ -32797,7 +33614,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.15">
-      <c r="A20" s="27"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="4" t="s">
         <v>367</v>
       </c>
@@ -32924,7 +33741,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -32932,1318 +33749,1516 @@
     <col min="3" max="3" width="31.5" customWidth="1"/>
     <col min="4" max="4" width="35.83203125" customWidth="1"/>
     <col min="5" max="5" width="56.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="42.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.83203125" customWidth="1"/>
     <col min="10" max="10" width="32.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
+    <col min="12" max="13" width="40" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="67.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="45.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="51" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="71" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.6640625" customWidth="1"/>
+    <col min="19" max="19" width="45.5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="41.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:21" ht="14" x14ac:dyDescent="0.15">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="S1" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="T1" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="U1" s="37"/>
+    </row>
+    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.15">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="14" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:21" ht="28" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="384" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-    </row>
-    <row r="4" spans="1:20" ht="306" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:21" ht="384" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="N4" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="R4" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="S4" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="T4" s="19" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="280" x14ac:dyDescent="0.15">
+      <c r="B4" s="4"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+    </row>
+    <row r="5" spans="1:21" ht="397" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>320</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="N5" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-    </row>
-    <row r="6" spans="1:20" ht="56" x14ac:dyDescent="0.15">
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="R5" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="T5" s="22" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="345" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+    </row>
+    <row r="7" spans="1:21" ht="70" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-    </row>
-    <row r="7" spans="1:20" ht="306" x14ac:dyDescent="0.15">
-      <c r="A7" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="M7" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="P7" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q7" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="R7" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="S7" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="T7" s="19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+    </row>
+    <row r="8" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="M8" s="21" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="M8" s="24" t="s">
         <v>416</v>
       </c>
+      <c r="N8" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="O8" s="21" t="s">
+        <v>418</v>
+      </c>
       <c r="P8" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q8" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="R8" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="S8" s="18" t="s">
+      <c r="Q8" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="T8" s="18" t="s">
+      <c r="R8" s="21" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="345" x14ac:dyDescent="0.15">
+      <c r="S8" s="25" t="s">
+        <v>422</v>
+      </c>
+      <c r="T8" s="22" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>325</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="O9" s="17"/>
-      <c r="P9" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="Q9" s="20" t="s">
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="R9" s="20" t="s">
+      <c r="M9" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="S9" s="20" t="s">
+      <c r="N9" s="22" t="s">
         <v>427</v>
       </c>
-      <c r="T9" s="19" t="s">
+      <c r="O9" s="22" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="P9" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="R9" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="T9" s="21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>325</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>430</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="O10" s="17"/>
-      <c r="P10" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q10" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="18" t="s">
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="22" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="293" x14ac:dyDescent="0.15">
+      <c r="O10" s="20"/>
+      <c r="P10" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q10" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="R10" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="S10" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="T10" s="22" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>325</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="20" t="s">
-        <v>437</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-    </row>
-    <row r="12" spans="1:20" ht="154" x14ac:dyDescent="0.15">
+        <v>58</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="26" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q11" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="21" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="19" t="s">
-        <v>442</v>
-      </c>
-      <c r="M12" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="N12" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="O12" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="P12" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="R12" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="S12" s="19" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="23" t="s">
         <v>449</v>
       </c>
-      <c r="T12" s="19" t="s">
+      <c r="O12" s="23" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="210" x14ac:dyDescent="0.15">
+      <c r="P12" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+    </row>
+    <row r="13" spans="1:21" ht="224" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="19" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="22" t="s">
         <v>454</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="M13" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="N13" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="P13" s="21" t="s">
+      <c r="O13" s="22" t="s">
         <v>457</v>
       </c>
-      <c r="Q13" s="19" t="s">
+      <c r="P13" s="24" t="s">
         <v>458</v>
       </c>
-      <c r="R13" s="18" t="s">
+      <c r="Q13" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="S13" s="18" t="s">
+      <c r="R13" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="T13" s="19" t="s">
+      <c r="S13" s="22" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="358" x14ac:dyDescent="0.15">
+      <c r="T13" s="22" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="306" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>336</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="O14" s="20" t="s">
+      <c r="M14" s="24" t="s">
         <v>466</v>
       </c>
-      <c r="P14" s="21" t="s">
+      <c r="N14" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="O14" s="22" t="s">
         <v>468</v>
       </c>
-      <c r="R14" s="20" t="s">
+      <c r="P14" s="24" t="s">
         <v>469</v>
       </c>
-      <c r="S14" s="19" t="s">
+      <c r="Q14" s="22" t="s">
         <v>470</v>
       </c>
-      <c r="T14" s="19" t="s">
+      <c r="R14" s="21" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="S14" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="T14" s="22" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>336</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>476</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="P15" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q15" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="S15" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="T15" s="22" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="M15" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="N15" s="19" t="s">
-        <v>475</v>
-      </c>
-      <c r="O15" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="P15" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q15" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="R15" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="S15" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="T15" s="19" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="358" x14ac:dyDescent="0.15">
-      <c r="A16" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="E16" s="19" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21" t="s">
         <v>484</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="M16" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="N16" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="I16" s="19" t="s">
+      <c r="O16" s="22" t="s">
         <v>488</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="P16" s="24" t="s">
         <v>489</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="Q16" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-    </row>
-    <row r="17" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="R16" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="S16" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="T16" s="22" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="358" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>493</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="D17" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="E17" s="22" t="s">
         <v>496</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="F17" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="G17" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="H17" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="K17" s="19" t="s">
+      <c r="I17" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-    </row>
-    <row r="18" spans="1:20" ht="358" x14ac:dyDescent="0.15">
+      <c r="J17" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+    </row>
+    <row r="18" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>347</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>501</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="E18" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="C18" s="22" t="s">
         <v>504</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="D18" s="22" t="s">
         <v>505</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="E18" s="22" t="s">
         <v>506</v>
       </c>
-      <c r="I18" s="21" t="s">
+      <c r="F18" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="G18" s="22" t="s">
         <v>508</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="H18" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-    </row>
-    <row r="19" spans="1:20" ht="371" x14ac:dyDescent="0.15">
+      <c r="I18" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>512</v>
+      </c>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+    </row>
+    <row r="19" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>347</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+    </row>
+    <row r="20" spans="1:20" ht="371" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>512</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>514</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-    </row>
-    <row r="20" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A20" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>521</v>
-      </c>
-      <c r="M20" s="19" t="s">
+      <c r="C20" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="N20" s="19" t="s">
+      <c r="D20" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="O20" s="19" t="s">
+      <c r="E20" s="22" t="s">
         <v>524</v>
       </c>
-      <c r="P20" s="20" t="s">
+      <c r="F20" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="Q20" s="19" t="s">
+      <c r="G20" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="R20" s="20" t="s">
+      <c r="H20" s="21" t="s">
         <v>527</v>
       </c>
-      <c r="S20" s="19" t="s">
+      <c r="I20" s="22" t="s">
         <v>528</v>
       </c>
-      <c r="T20" s="19" t="s">
+      <c r="J20" s="21" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="319" x14ac:dyDescent="0.15">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+    </row>
+    <row r="21" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="27" t="s">
         <v>531</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="F21" s="21" t="s">
         <v>532</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="18" t="s">
+      <c r="G21" s="21" t="s">
         <v>533</v>
       </c>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="M21" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="N21" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="O21" s="28" t="s">
+        <v>539</v>
+      </c>
+      <c r="P21" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q21" s="28" t="s">
+        <v>541</v>
+      </c>
+      <c r="R21" s="22" t="s">
+        <v>542</v>
+      </c>
+      <c r="S21" s="22" t="s">
+        <v>543</v>
+      </c>
+      <c r="T21" s="28" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="22" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>537</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>538</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>540</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>541</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>542</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>543</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-    </row>
-    <row r="23" spans="1:20" ht="371" x14ac:dyDescent="0.15">
+        <v>282</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="22" t="s">
+        <v>545</v>
+      </c>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="M22" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="N22" s="22" t="s">
+        <v>549</v>
+      </c>
+      <c r="O22" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="P22" s="23" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q22" s="22" t="s">
+        <v>552</v>
+      </c>
+      <c r="R22" s="23" t="s">
+        <v>553</v>
+      </c>
+      <c r="S22" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="T22" s="22" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>545</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>546</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18" t="s">
-        <v>547</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="19" t="s">
-        <v>549</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>550</v>
-      </c>
-      <c r="K23" s="17"/>
-      <c r="L23" s="19" t="s">
-        <v>551</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="N23" s="17"/>
-      <c r="O23" s="19" t="s">
-        <v>553</v>
-      </c>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="18" t="s">
-        <v>554</v>
-      </c>
-      <c r="R23" s="17"/>
-      <c r="S23" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="T23" s="17"/>
-    </row>
-    <row r="24" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+        <v>74</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="22" t="s">
+        <v>556</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+    </row>
+    <row r="24" spans="1:20" ht="306" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>558</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>559</v>
-      </c>
-      <c r="G24" s="19" t="s">
         <v>560</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="C24" s="22" t="s">
         <v>561</v>
       </c>
-      <c r="I24" s="19" t="s">
+      <c r="D24" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="E24" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="F24" s="29" t="s">
         <v>564</v>
       </c>
-      <c r="L24" s="19" t="s">
+      <c r="G24" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="H24" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="N24" s="19" t="s">
+      <c r="I24" s="22" t="s">
         <v>567</v>
       </c>
-      <c r="O24" s="19" t="s">
+      <c r="J24" s="4"/>
+      <c r="K24" s="28" t="s">
         <v>568</v>
       </c>
-      <c r="P24" s="20" t="s">
+      <c r="L24" s="28" t="s">
         <v>569</v>
       </c>
-      <c r="Q24" s="20" t="s">
+      <c r="M24" s="30" t="s">
         <v>570</v>
       </c>
-      <c r="R24" s="20" t="s">
+      <c r="N24" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="S24" s="19" t="s">
+      <c r="O24" s="28" t="s">
         <v>572</v>
       </c>
-      <c r="T24" s="20" t="s">
+      <c r="P24" s="23" t="s">
         <v>573</v>
+      </c>
+      <c r="Q24" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="R24" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="S24" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="T24" s="28" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="F25" s="20" t="s">
         <v>578</v>
       </c>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="20" t="s">
+      <c r="C25" s="22" t="s">
         <v>579</v>
       </c>
-      <c r="M25" s="19" t="s">
+      <c r="D25" s="21" t="s">
         <v>580</v>
       </c>
-      <c r="N25" s="19" t="s">
+      <c r="E25" s="21" t="s">
         <v>581</v>
       </c>
-      <c r="O25" s="17"/>
-      <c r="P25" s="20" t="s">
+      <c r="F25" s="21" t="s">
         <v>582</v>
       </c>
-      <c r="Q25" s="20" t="s">
+      <c r="G25" s="22" t="s">
         <v>583</v>
       </c>
-      <c r="R25" s="20" t="s">
+      <c r="H25" s="22" t="s">
         <v>584</v>
       </c>
-      <c r="S25" s="20" t="s">
+      <c r="I25" s="22" t="s">
         <v>585</v>
       </c>
-      <c r="T25" s="20" t="s">
+      <c r="J25" s="22" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" ht="50.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:20" ht="98.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:20" ht="55.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:20" ht="13" x14ac:dyDescent="0.15">
-      <c r="F31" s="24"/>
+      <c r="K25" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+    </row>
+    <row r="26" spans="1:20" ht="371" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>591</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="22" t="s">
+        <v>592</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>593</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="22" t="s">
+        <v>594</v>
+      </c>
+      <c r="M26" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="N26" s="20"/>
+      <c r="O26" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="R26" s="20"/>
+      <c r="S26" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="T26" s="20"/>
+    </row>
+    <row r="27" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>602</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="M27" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="N27" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="O27" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="P27" s="23" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q27" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="R27" s="23" t="s">
+        <v>614</v>
+      </c>
+      <c r="S27" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="T27" s="23" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>619</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>620</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>621</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="23" t="s">
+        <v>622</v>
+      </c>
+      <c r="M28" s="22" t="s">
+        <v>623</v>
+      </c>
+      <c r="N28" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="O28" s="20"/>
+      <c r="P28" s="23" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q28" s="23" t="s">
+        <v>626</v>
+      </c>
+      <c r="R28" s="23" t="s">
+        <v>627</v>
+      </c>
+      <c r="S28" s="23" t="s">
+        <v>628</v>
+      </c>
+      <c r="T28" s="23" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="13" x14ac:dyDescent="0.15">
+      <c r="S29" s="31" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="98.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" spans="6:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" spans="6:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="F34" s="32"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="T1:U1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="M3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="E4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="L4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="M4" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="N4" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="O4" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="P4" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="Q4" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="R4" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="S4" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="T4" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="M5" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="N5" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="P5" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
-    <hyperlink ref="Q6" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
-    <hyperlink ref="E7" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
-    <hyperlink ref="L7" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
-    <hyperlink ref="M7" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
-    <hyperlink ref="N7" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
-    <hyperlink ref="O7" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
-    <hyperlink ref="P7" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
-    <hyperlink ref="Q7" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
-    <hyperlink ref="R7" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
-    <hyperlink ref="S7" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
-    <hyperlink ref="T7" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
-    <hyperlink ref="E8" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
-    <hyperlink ref="L8" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
-    <hyperlink ref="M8" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
-    <hyperlink ref="N8" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
-    <hyperlink ref="O8" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
-    <hyperlink ref="P8" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
-    <hyperlink ref="Q8" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
-    <hyperlink ref="R8" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
-    <hyperlink ref="S8" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
-    <hyperlink ref="T8" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
-    <hyperlink ref="G9" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
-    <hyperlink ref="N9" r:id="rId37" xr:uid="{00000000-0004-0000-0200-000024000000}"/>
-    <hyperlink ref="P9" r:id="rId38" xr:uid="{00000000-0004-0000-0200-000025000000}"/>
-    <hyperlink ref="Q9" r:id="rId39" xr:uid="{00000000-0004-0000-0200-000026000000}"/>
-    <hyperlink ref="R9" r:id="rId40" xr:uid="{00000000-0004-0000-0200-000027000000}"/>
-    <hyperlink ref="S9" r:id="rId41" xr:uid="{00000000-0004-0000-0200-000028000000}"/>
-    <hyperlink ref="T9" r:id="rId42" xr:uid="{00000000-0004-0000-0200-000029000000}"/>
-    <hyperlink ref="D10" r:id="rId43" xr:uid="{00000000-0004-0000-0200-00002A000000}"/>
-    <hyperlink ref="E10" r:id="rId44" xr:uid="{00000000-0004-0000-0200-00002B000000}"/>
-    <hyperlink ref="G10" r:id="rId45" xr:uid="{00000000-0004-0000-0200-00002C000000}"/>
-    <hyperlink ref="N10" r:id="rId46" xr:uid="{00000000-0004-0000-0200-00002D000000}"/>
-    <hyperlink ref="Q10" r:id="rId47" xr:uid="{00000000-0004-0000-0200-00002E000000}"/>
-    <hyperlink ref="T10" r:id="rId48" xr:uid="{00000000-0004-0000-0200-00002F000000}"/>
-    <hyperlink ref="N11" r:id="rId49" xr:uid="{00000000-0004-0000-0200-000030000000}"/>
-    <hyperlink ref="O11" r:id="rId50" xr:uid="{00000000-0004-0000-0200-000031000000}"/>
-    <hyperlink ref="P11" r:id="rId51" xr:uid="{00000000-0004-0000-0200-000032000000}"/>
-    <hyperlink ref="R11" r:id="rId52" xr:uid="{00000000-0004-0000-0200-000033000000}"/>
-    <hyperlink ref="E12" r:id="rId53" xr:uid="{00000000-0004-0000-0200-000034000000}"/>
-    <hyperlink ref="L12" r:id="rId54" xr:uid="{00000000-0004-0000-0200-000035000000}"/>
-    <hyperlink ref="M12" r:id="rId55" xr:uid="{00000000-0004-0000-0200-000036000000}"/>
-    <hyperlink ref="N12" r:id="rId56" xr:uid="{00000000-0004-0000-0200-000037000000}"/>
-    <hyperlink ref="O12" r:id="rId57" xr:uid="{00000000-0004-0000-0200-000038000000}"/>
-    <hyperlink ref="P12" r:id="rId58" xr:uid="{00000000-0004-0000-0200-000039000000}"/>
-    <hyperlink ref="Q12" r:id="rId59" xr:uid="{00000000-0004-0000-0200-00003A000000}"/>
-    <hyperlink ref="R12" r:id="rId60" xr:uid="{00000000-0004-0000-0200-00003B000000}"/>
-    <hyperlink ref="S12" r:id="rId61" xr:uid="{00000000-0004-0000-0200-00003C000000}"/>
-    <hyperlink ref="T12" r:id="rId62" xr:uid="{00000000-0004-0000-0200-00003D000000}"/>
-    <hyperlink ref="E13" r:id="rId63" xr:uid="{00000000-0004-0000-0200-00003E000000}"/>
-    <hyperlink ref="L13" r:id="rId64" xr:uid="{00000000-0004-0000-0200-00003F000000}"/>
-    <hyperlink ref="M13" r:id="rId65" xr:uid="{00000000-0004-0000-0200-000040000000}"/>
-    <hyperlink ref="N13" r:id="rId66" xr:uid="{00000000-0004-0000-0200-000041000000}"/>
-    <hyperlink ref="O13" r:id="rId67" xr:uid="{00000000-0004-0000-0200-000042000000}"/>
-    <hyperlink ref="P13" r:id="rId68" xr:uid="{00000000-0004-0000-0200-000043000000}"/>
-    <hyperlink ref="Q13" r:id="rId69" xr:uid="{00000000-0004-0000-0200-000044000000}"/>
-    <hyperlink ref="R13" r:id="rId70" xr:uid="{00000000-0004-0000-0200-000045000000}"/>
-    <hyperlink ref="S13" r:id="rId71" xr:uid="{00000000-0004-0000-0200-000046000000}"/>
-    <hyperlink ref="T13" r:id="rId72" xr:uid="{00000000-0004-0000-0200-000047000000}"/>
-    <hyperlink ref="E14" r:id="rId73" xr:uid="{00000000-0004-0000-0200-000048000000}"/>
-    <hyperlink ref="L14" r:id="rId74" xr:uid="{00000000-0004-0000-0200-000049000000}"/>
-    <hyperlink ref="M14" r:id="rId75" xr:uid="{00000000-0004-0000-0200-00004A000000}"/>
-    <hyperlink ref="N14" r:id="rId76" xr:uid="{00000000-0004-0000-0200-00004B000000}"/>
-    <hyperlink ref="O14" r:id="rId77" xr:uid="{00000000-0004-0000-0200-00004C000000}"/>
-    <hyperlink ref="P14" r:id="rId78" xr:uid="{00000000-0004-0000-0200-00004D000000}"/>
-    <hyperlink ref="Q14" r:id="rId79" xr:uid="{00000000-0004-0000-0200-00004E000000}"/>
-    <hyperlink ref="R14" r:id="rId80" xr:uid="{00000000-0004-0000-0200-00004F000000}"/>
-    <hyperlink ref="S14" r:id="rId81" xr:uid="{00000000-0004-0000-0200-000050000000}"/>
-    <hyperlink ref="T14" r:id="rId82" xr:uid="{00000000-0004-0000-0200-000051000000}"/>
-    <hyperlink ref="E15" r:id="rId83" xr:uid="{00000000-0004-0000-0200-000052000000}"/>
-    <hyperlink ref="L15" r:id="rId84" xr:uid="{00000000-0004-0000-0200-000053000000}"/>
-    <hyperlink ref="M15" r:id="rId85" xr:uid="{00000000-0004-0000-0200-000054000000}"/>
-    <hyperlink ref="N15" r:id="rId86" xr:uid="{00000000-0004-0000-0200-000055000000}"/>
-    <hyperlink ref="O15" r:id="rId87" xr:uid="{00000000-0004-0000-0200-000056000000}"/>
-    <hyperlink ref="P15" r:id="rId88" xr:uid="{00000000-0004-0000-0200-000057000000}"/>
-    <hyperlink ref="R15" r:id="rId89" xr:uid="{00000000-0004-0000-0200-000058000000}"/>
-    <hyperlink ref="S15" r:id="rId90" xr:uid="{00000000-0004-0000-0200-000059000000}"/>
-    <hyperlink ref="T15" r:id="rId91" xr:uid="{00000000-0004-0000-0200-00005A000000}"/>
-    <hyperlink ref="C16" r:id="rId92" xr:uid="{00000000-0004-0000-0200-00005B000000}"/>
-    <hyperlink ref="D16" r:id="rId93" xr:uid="{00000000-0004-0000-0200-00005C000000}"/>
-    <hyperlink ref="E16" r:id="rId94" xr:uid="{00000000-0004-0000-0200-00005D000000}"/>
-    <hyperlink ref="F16" r:id="rId95" xr:uid="{00000000-0004-0000-0200-00005E000000}"/>
-    <hyperlink ref="G16" r:id="rId96" xr:uid="{00000000-0004-0000-0200-00005F000000}"/>
-    <hyperlink ref="H16" r:id="rId97" xr:uid="{00000000-0004-0000-0200-000060000000}"/>
-    <hyperlink ref="I16" r:id="rId98" xr:uid="{00000000-0004-0000-0200-000061000000}"/>
-    <hyperlink ref="J16" r:id="rId99" xr:uid="{00000000-0004-0000-0200-000062000000}"/>
-    <hyperlink ref="K16" r:id="rId100" xr:uid="{00000000-0004-0000-0200-000063000000}"/>
-    <hyperlink ref="C17" r:id="rId101" xr:uid="{00000000-0004-0000-0200-000064000000}"/>
-    <hyperlink ref="D17" r:id="rId102" xr:uid="{00000000-0004-0000-0200-000065000000}"/>
-    <hyperlink ref="E17" r:id="rId103" xr:uid="{00000000-0004-0000-0200-000066000000}"/>
-    <hyperlink ref="F17" r:id="rId104" xr:uid="{00000000-0004-0000-0200-000067000000}"/>
-    <hyperlink ref="G17" r:id="rId105" xr:uid="{00000000-0004-0000-0200-000068000000}"/>
-    <hyperlink ref="H17" r:id="rId106" xr:uid="{00000000-0004-0000-0200-000069000000}"/>
-    <hyperlink ref="I17" r:id="rId107" xr:uid="{00000000-0004-0000-0200-00006A000000}"/>
-    <hyperlink ref="J17" r:id="rId108" xr:uid="{00000000-0004-0000-0200-00006B000000}"/>
-    <hyperlink ref="K17" r:id="rId109" xr:uid="{00000000-0004-0000-0200-00006C000000}"/>
-    <hyperlink ref="C18" r:id="rId110" xr:uid="{00000000-0004-0000-0200-00006D000000}"/>
-    <hyperlink ref="D18" r:id="rId111" xr:uid="{00000000-0004-0000-0200-00006E000000}"/>
-    <hyperlink ref="E18" r:id="rId112" xr:uid="{00000000-0004-0000-0200-00006F000000}"/>
-    <hyperlink ref="F18" r:id="rId113" xr:uid="{00000000-0004-0000-0200-000070000000}"/>
-    <hyperlink ref="G18" r:id="rId114" xr:uid="{00000000-0004-0000-0200-000071000000}"/>
-    <hyperlink ref="H18" r:id="rId115" xr:uid="{00000000-0004-0000-0200-000072000000}"/>
-    <hyperlink ref="I18" r:id="rId116" xr:uid="{00000000-0004-0000-0200-000073000000}"/>
-    <hyperlink ref="J18" r:id="rId117" xr:uid="{00000000-0004-0000-0200-000074000000}"/>
-    <hyperlink ref="K18" r:id="rId118" xr:uid="{00000000-0004-0000-0200-000075000000}"/>
-    <hyperlink ref="C19" r:id="rId119" xr:uid="{00000000-0004-0000-0200-000076000000}"/>
-    <hyperlink ref="D19" r:id="rId120" xr:uid="{00000000-0004-0000-0200-000077000000}"/>
-    <hyperlink ref="E19" r:id="rId121" xr:uid="{00000000-0004-0000-0200-000078000000}"/>
-    <hyperlink ref="F19" r:id="rId122" xr:uid="{00000000-0004-0000-0200-000079000000}"/>
-    <hyperlink ref="G19" r:id="rId123" xr:uid="{00000000-0004-0000-0200-00007A000000}"/>
-    <hyperlink ref="H19" r:id="rId124" xr:uid="{00000000-0004-0000-0200-00007B000000}"/>
-    <hyperlink ref="I19" r:id="rId125" xr:uid="{00000000-0004-0000-0200-00007C000000}"/>
-    <hyperlink ref="J19" r:id="rId126" xr:uid="{00000000-0004-0000-0200-00007D000000}"/>
-    <hyperlink ref="E20" r:id="rId127" xr:uid="{00000000-0004-0000-0200-00007E000000}"/>
-    <hyperlink ref="K20" r:id="rId128" xr:uid="{00000000-0004-0000-0200-00007F000000}"/>
-    <hyperlink ref="L20" r:id="rId129" xr:uid="{00000000-0004-0000-0200-000080000000}"/>
-    <hyperlink ref="M20" r:id="rId130" xr:uid="{00000000-0004-0000-0200-000081000000}"/>
-    <hyperlink ref="N20" r:id="rId131" xr:uid="{00000000-0004-0000-0200-000082000000}"/>
-    <hyperlink ref="O20" r:id="rId132" xr:uid="{00000000-0004-0000-0200-000083000000}"/>
-    <hyperlink ref="P20" r:id="rId133" xr:uid="{00000000-0004-0000-0200-000084000000}"/>
-    <hyperlink ref="Q20" r:id="rId134" xr:uid="{00000000-0004-0000-0200-000085000000}"/>
-    <hyperlink ref="R20" r:id="rId135" xr:uid="{00000000-0004-0000-0200-000086000000}"/>
-    <hyperlink ref="S20" r:id="rId136" xr:uid="{00000000-0004-0000-0200-000087000000}"/>
-    <hyperlink ref="T20" r:id="rId137" xr:uid="{00000000-0004-0000-0200-000088000000}"/>
-    <hyperlink ref="E21" r:id="rId138" xr:uid="{00000000-0004-0000-0200-000089000000}"/>
-    <hyperlink ref="F21" r:id="rId139" xr:uid="{00000000-0004-0000-0200-00008A000000}"/>
-    <hyperlink ref="G21" r:id="rId140" xr:uid="{00000000-0004-0000-0200-00008B000000}"/>
-    <hyperlink ref="J21" r:id="rId141" xr:uid="{00000000-0004-0000-0200-00008C000000}"/>
-    <hyperlink ref="C22" r:id="rId142" xr:uid="{00000000-0004-0000-0200-00008D000000}"/>
-    <hyperlink ref="D22" r:id="rId143" xr:uid="{00000000-0004-0000-0200-00008E000000}"/>
-    <hyperlink ref="E22" r:id="rId144" xr:uid="{00000000-0004-0000-0200-00008F000000}"/>
-    <hyperlink ref="F22" r:id="rId145" xr:uid="{00000000-0004-0000-0200-000090000000}"/>
-    <hyperlink ref="G22" r:id="rId146" xr:uid="{00000000-0004-0000-0200-000091000000}"/>
-    <hyperlink ref="H22" r:id="rId147" xr:uid="{00000000-0004-0000-0200-000092000000}"/>
-    <hyperlink ref="I22" r:id="rId148" xr:uid="{00000000-0004-0000-0200-000093000000}"/>
-    <hyperlink ref="J22" r:id="rId149" xr:uid="{00000000-0004-0000-0200-000094000000}"/>
-    <hyperlink ref="K22" r:id="rId150" xr:uid="{00000000-0004-0000-0200-000095000000}"/>
-    <hyperlink ref="C23" r:id="rId151" xr:uid="{00000000-0004-0000-0200-000096000000}"/>
-    <hyperlink ref="D23" r:id="rId152" xr:uid="{00000000-0004-0000-0200-000097000000}"/>
-    <hyperlink ref="F23" r:id="rId153" xr:uid="{00000000-0004-0000-0200-000098000000}"/>
-    <hyperlink ref="G23" r:id="rId154" xr:uid="{00000000-0004-0000-0200-000099000000}"/>
-    <hyperlink ref="I23" r:id="rId155" xr:uid="{00000000-0004-0000-0200-00009A000000}"/>
-    <hyperlink ref="J23" r:id="rId156" xr:uid="{00000000-0004-0000-0200-00009B000000}"/>
-    <hyperlink ref="L23" r:id="rId157" xr:uid="{00000000-0004-0000-0200-00009C000000}"/>
-    <hyperlink ref="M23" r:id="rId158" xr:uid="{00000000-0004-0000-0200-00009D000000}"/>
-    <hyperlink ref="O23" r:id="rId159" xr:uid="{00000000-0004-0000-0200-00009E000000}"/>
-    <hyperlink ref="Q23" r:id="rId160" xr:uid="{00000000-0004-0000-0200-00009F000000}"/>
-    <hyperlink ref="S23" r:id="rId161" xr:uid="{00000000-0004-0000-0200-0000A0000000}"/>
-    <hyperlink ref="C24" r:id="rId162" xr:uid="{00000000-0004-0000-0200-0000A1000000}"/>
-    <hyperlink ref="D24" r:id="rId163" xr:uid="{00000000-0004-0000-0200-0000A2000000}"/>
-    <hyperlink ref="E24" r:id="rId164" xr:uid="{00000000-0004-0000-0200-0000A3000000}"/>
-    <hyperlink ref="F24" r:id="rId165" xr:uid="{00000000-0004-0000-0200-0000A4000000}"/>
-    <hyperlink ref="G24" r:id="rId166" xr:uid="{00000000-0004-0000-0200-0000A5000000}"/>
-    <hyperlink ref="H24" r:id="rId167" xr:uid="{00000000-0004-0000-0200-0000A6000000}"/>
-    <hyperlink ref="I24" r:id="rId168" xr:uid="{00000000-0004-0000-0200-0000A7000000}"/>
-    <hyperlink ref="J24" r:id="rId169" xr:uid="{00000000-0004-0000-0200-0000A8000000}"/>
-    <hyperlink ref="K24" r:id="rId170" xr:uid="{00000000-0004-0000-0200-0000A9000000}"/>
-    <hyperlink ref="L24" r:id="rId171" xr:uid="{00000000-0004-0000-0200-0000AA000000}"/>
-    <hyperlink ref="M24" r:id="rId172" xr:uid="{00000000-0004-0000-0200-0000AB000000}"/>
-    <hyperlink ref="N24" r:id="rId173" xr:uid="{00000000-0004-0000-0200-0000AC000000}"/>
-    <hyperlink ref="O24" r:id="rId174" xr:uid="{00000000-0004-0000-0200-0000AD000000}"/>
-    <hyperlink ref="P24" r:id="rId175" xr:uid="{00000000-0004-0000-0200-0000AE000000}"/>
-    <hyperlink ref="Q24" r:id="rId176" xr:uid="{00000000-0004-0000-0200-0000AF000000}"/>
-    <hyperlink ref="R24" r:id="rId177" xr:uid="{00000000-0004-0000-0200-0000B0000000}"/>
-    <hyperlink ref="S24" r:id="rId178" xr:uid="{00000000-0004-0000-0200-0000B1000000}"/>
-    <hyperlink ref="T24" r:id="rId179" xr:uid="{00000000-0004-0000-0200-0000B2000000}"/>
-    <hyperlink ref="C25" r:id="rId180" xr:uid="{00000000-0004-0000-0200-0000B3000000}"/>
-    <hyperlink ref="D25" r:id="rId181" xr:uid="{00000000-0004-0000-0200-0000B4000000}"/>
-    <hyperlink ref="E25" r:id="rId182" xr:uid="{00000000-0004-0000-0200-0000B5000000}"/>
-    <hyperlink ref="F25" r:id="rId183" xr:uid="{00000000-0004-0000-0200-0000B6000000}"/>
-    <hyperlink ref="L25" r:id="rId184" xr:uid="{00000000-0004-0000-0200-0000B7000000}"/>
-    <hyperlink ref="M25" r:id="rId185" xr:uid="{00000000-0004-0000-0200-0000B8000000}"/>
-    <hyperlink ref="N25" r:id="rId186" xr:uid="{00000000-0004-0000-0200-0000B9000000}"/>
-    <hyperlink ref="P25" r:id="rId187" xr:uid="{00000000-0004-0000-0200-0000BA000000}"/>
-    <hyperlink ref="Q25" r:id="rId188" xr:uid="{00000000-0004-0000-0200-0000BB000000}"/>
-    <hyperlink ref="R25" r:id="rId189" xr:uid="{00000000-0004-0000-0200-0000BC000000}"/>
-    <hyperlink ref="S25" r:id="rId190" xr:uid="{00000000-0004-0000-0200-0000BD000000}"/>
-    <hyperlink ref="T25" r:id="rId191" xr:uid="{00000000-0004-0000-0200-0000BE000000}"/>
+    <hyperlink ref="M4" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="N5" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="O5" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="P5" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="Q5" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="R5" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="S5" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="T5" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="M6" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="N6" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="P6" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
+    <hyperlink ref="Q7" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
+    <hyperlink ref="E8" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
+    <hyperlink ref="L8" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
+    <hyperlink ref="M8" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
+    <hyperlink ref="N8" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
+    <hyperlink ref="O8" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
+    <hyperlink ref="P8" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
+    <hyperlink ref="Q8" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
+    <hyperlink ref="R8" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
+    <hyperlink ref="S8" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
+    <hyperlink ref="T8" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
+    <hyperlink ref="E9" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
+    <hyperlink ref="L9" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
+    <hyperlink ref="M9" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
+    <hyperlink ref="N9" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
+    <hyperlink ref="O9" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
+    <hyperlink ref="P9" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
+    <hyperlink ref="Q9" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
+    <hyperlink ref="R9" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
+    <hyperlink ref="S9" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
+    <hyperlink ref="T9" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
+    <hyperlink ref="G10" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
+    <hyperlink ref="N10" r:id="rId37" xr:uid="{00000000-0004-0000-0200-000024000000}"/>
+    <hyperlink ref="P10" r:id="rId38" xr:uid="{00000000-0004-0000-0200-000025000000}"/>
+    <hyperlink ref="Q10" r:id="rId39" xr:uid="{00000000-0004-0000-0200-000026000000}"/>
+    <hyperlink ref="R10" r:id="rId40" xr:uid="{00000000-0004-0000-0200-000027000000}"/>
+    <hyperlink ref="S10" r:id="rId41" xr:uid="{00000000-0004-0000-0200-000028000000}"/>
+    <hyperlink ref="T10" r:id="rId42" xr:uid="{00000000-0004-0000-0200-000029000000}"/>
+    <hyperlink ref="D11" r:id="rId43" xr:uid="{00000000-0004-0000-0200-00002A000000}"/>
+    <hyperlink ref="E11" r:id="rId44" xr:uid="{00000000-0004-0000-0200-00002B000000}"/>
+    <hyperlink ref="G11" r:id="rId45" xr:uid="{00000000-0004-0000-0200-00002C000000}"/>
+    <hyperlink ref="N11" r:id="rId46" xr:uid="{00000000-0004-0000-0200-00002D000000}"/>
+    <hyperlink ref="Q11" r:id="rId47" xr:uid="{00000000-0004-0000-0200-00002E000000}"/>
+    <hyperlink ref="T11" r:id="rId48" xr:uid="{00000000-0004-0000-0200-00002F000000}"/>
+    <hyperlink ref="N12" r:id="rId49" xr:uid="{00000000-0004-0000-0200-000030000000}"/>
+    <hyperlink ref="O12" r:id="rId50" xr:uid="{00000000-0004-0000-0200-000031000000}"/>
+    <hyperlink ref="P12" r:id="rId51" xr:uid="{00000000-0004-0000-0200-000032000000}"/>
+    <hyperlink ref="R12" r:id="rId52" xr:uid="{00000000-0004-0000-0200-000033000000}"/>
+    <hyperlink ref="E13" r:id="rId53" xr:uid="{00000000-0004-0000-0200-000034000000}"/>
+    <hyperlink ref="L13" r:id="rId54" xr:uid="{00000000-0004-0000-0200-000035000000}"/>
+    <hyperlink ref="M13" r:id="rId55" xr:uid="{00000000-0004-0000-0200-000036000000}"/>
+    <hyperlink ref="N13" r:id="rId56" xr:uid="{00000000-0004-0000-0200-000037000000}"/>
+    <hyperlink ref="O13" r:id="rId57" xr:uid="{00000000-0004-0000-0200-000038000000}"/>
+    <hyperlink ref="P13" r:id="rId58" xr:uid="{00000000-0004-0000-0200-000039000000}"/>
+    <hyperlink ref="Q13" r:id="rId59" xr:uid="{00000000-0004-0000-0200-00003A000000}"/>
+    <hyperlink ref="R13" r:id="rId60" xr:uid="{00000000-0004-0000-0200-00003B000000}"/>
+    <hyperlink ref="S13" r:id="rId61" xr:uid="{00000000-0004-0000-0200-00003C000000}"/>
+    <hyperlink ref="T13" r:id="rId62" xr:uid="{00000000-0004-0000-0200-00003D000000}"/>
+    <hyperlink ref="E14" r:id="rId63" xr:uid="{00000000-0004-0000-0200-00003E000000}"/>
+    <hyperlink ref="L14" r:id="rId64" xr:uid="{00000000-0004-0000-0200-00003F000000}"/>
+    <hyperlink ref="M14" r:id="rId65" xr:uid="{00000000-0004-0000-0200-000040000000}"/>
+    <hyperlink ref="N14" r:id="rId66" xr:uid="{00000000-0004-0000-0200-000041000000}"/>
+    <hyperlink ref="O14" r:id="rId67" xr:uid="{00000000-0004-0000-0200-000042000000}"/>
+    <hyperlink ref="P14" r:id="rId68" xr:uid="{00000000-0004-0000-0200-000043000000}"/>
+    <hyperlink ref="Q14" r:id="rId69" xr:uid="{00000000-0004-0000-0200-000044000000}"/>
+    <hyperlink ref="R14" r:id="rId70" xr:uid="{00000000-0004-0000-0200-000045000000}"/>
+    <hyperlink ref="S14" r:id="rId71" xr:uid="{00000000-0004-0000-0200-000046000000}"/>
+    <hyperlink ref="T14" r:id="rId72" xr:uid="{00000000-0004-0000-0200-000047000000}"/>
+    <hyperlink ref="E15" r:id="rId73" xr:uid="{00000000-0004-0000-0200-000048000000}"/>
+    <hyperlink ref="L15" r:id="rId74" xr:uid="{00000000-0004-0000-0200-000049000000}"/>
+    <hyperlink ref="M15" r:id="rId75" xr:uid="{00000000-0004-0000-0200-00004A000000}"/>
+    <hyperlink ref="N15" r:id="rId76" xr:uid="{00000000-0004-0000-0200-00004B000000}"/>
+    <hyperlink ref="O15" r:id="rId77" xr:uid="{00000000-0004-0000-0200-00004C000000}"/>
+    <hyperlink ref="P15" r:id="rId78" xr:uid="{00000000-0004-0000-0200-00004D000000}"/>
+    <hyperlink ref="Q15" r:id="rId79" xr:uid="{00000000-0004-0000-0200-00004E000000}"/>
+    <hyperlink ref="R15" r:id="rId80" xr:uid="{00000000-0004-0000-0200-00004F000000}"/>
+    <hyperlink ref="S15" r:id="rId81" xr:uid="{00000000-0004-0000-0200-000050000000}"/>
+    <hyperlink ref="T15" r:id="rId82" xr:uid="{00000000-0004-0000-0200-000051000000}"/>
+    <hyperlink ref="E16" r:id="rId83" xr:uid="{00000000-0004-0000-0200-000052000000}"/>
+    <hyperlink ref="L16" r:id="rId84" xr:uid="{00000000-0004-0000-0200-000053000000}"/>
+    <hyperlink ref="M16" r:id="rId85" xr:uid="{00000000-0004-0000-0200-000054000000}"/>
+    <hyperlink ref="N16" r:id="rId86" xr:uid="{00000000-0004-0000-0200-000055000000}"/>
+    <hyperlink ref="O16" r:id="rId87" xr:uid="{00000000-0004-0000-0200-000056000000}"/>
+    <hyperlink ref="P16" r:id="rId88" xr:uid="{00000000-0004-0000-0200-000057000000}"/>
+    <hyperlink ref="R16" r:id="rId89" xr:uid="{00000000-0004-0000-0200-000058000000}"/>
+    <hyperlink ref="S16" r:id="rId90" xr:uid="{00000000-0004-0000-0200-000059000000}"/>
+    <hyperlink ref="T16" r:id="rId91" xr:uid="{00000000-0004-0000-0200-00005A000000}"/>
+    <hyperlink ref="C17" r:id="rId92" xr:uid="{00000000-0004-0000-0200-00005B000000}"/>
+    <hyperlink ref="D17" r:id="rId93" xr:uid="{00000000-0004-0000-0200-00005C000000}"/>
+    <hyperlink ref="E17" r:id="rId94" xr:uid="{00000000-0004-0000-0200-00005D000000}"/>
+    <hyperlink ref="F17" r:id="rId95" xr:uid="{00000000-0004-0000-0200-00005E000000}"/>
+    <hyperlink ref="G17" r:id="rId96" xr:uid="{00000000-0004-0000-0200-00005F000000}"/>
+    <hyperlink ref="H17" r:id="rId97" xr:uid="{00000000-0004-0000-0200-000060000000}"/>
+    <hyperlink ref="I17" r:id="rId98" xr:uid="{00000000-0004-0000-0200-000061000000}"/>
+    <hyperlink ref="J17" r:id="rId99" xr:uid="{00000000-0004-0000-0200-000062000000}"/>
+    <hyperlink ref="K17" r:id="rId100" xr:uid="{00000000-0004-0000-0200-000063000000}"/>
+    <hyperlink ref="C18" r:id="rId101" xr:uid="{00000000-0004-0000-0200-000064000000}"/>
+    <hyperlink ref="D18" r:id="rId102" xr:uid="{00000000-0004-0000-0200-000065000000}"/>
+    <hyperlink ref="E18" r:id="rId103" xr:uid="{00000000-0004-0000-0200-000066000000}"/>
+    <hyperlink ref="F18" r:id="rId104" xr:uid="{00000000-0004-0000-0200-000067000000}"/>
+    <hyperlink ref="G18" r:id="rId105" xr:uid="{00000000-0004-0000-0200-000068000000}"/>
+    <hyperlink ref="H18" r:id="rId106" xr:uid="{00000000-0004-0000-0200-000069000000}"/>
+    <hyperlink ref="I18" r:id="rId107" xr:uid="{00000000-0004-0000-0200-00006A000000}"/>
+    <hyperlink ref="J18" r:id="rId108" xr:uid="{00000000-0004-0000-0200-00006B000000}"/>
+    <hyperlink ref="K18" r:id="rId109" xr:uid="{00000000-0004-0000-0200-00006C000000}"/>
+    <hyperlink ref="C19" r:id="rId110" xr:uid="{00000000-0004-0000-0200-00006D000000}"/>
+    <hyperlink ref="D19" r:id="rId111" xr:uid="{00000000-0004-0000-0200-00006E000000}"/>
+    <hyperlink ref="E19" r:id="rId112" xr:uid="{00000000-0004-0000-0200-00006F000000}"/>
+    <hyperlink ref="F19" r:id="rId113" xr:uid="{00000000-0004-0000-0200-000070000000}"/>
+    <hyperlink ref="G19" r:id="rId114" xr:uid="{00000000-0004-0000-0200-000071000000}"/>
+    <hyperlink ref="H19" r:id="rId115" xr:uid="{00000000-0004-0000-0200-000072000000}"/>
+    <hyperlink ref="I19" r:id="rId116" xr:uid="{00000000-0004-0000-0200-000073000000}"/>
+    <hyperlink ref="J19" r:id="rId117" xr:uid="{00000000-0004-0000-0200-000074000000}"/>
+    <hyperlink ref="K19" r:id="rId118" xr:uid="{00000000-0004-0000-0200-000075000000}"/>
+    <hyperlink ref="C20" r:id="rId119" xr:uid="{00000000-0004-0000-0200-000076000000}"/>
+    <hyperlink ref="D20" r:id="rId120" xr:uid="{00000000-0004-0000-0200-000077000000}"/>
+    <hyperlink ref="E20" r:id="rId121" xr:uid="{00000000-0004-0000-0200-000078000000}"/>
+    <hyperlink ref="F20" r:id="rId122" xr:uid="{00000000-0004-0000-0200-000079000000}"/>
+    <hyperlink ref="G20" r:id="rId123" xr:uid="{00000000-0004-0000-0200-00007A000000}"/>
+    <hyperlink ref="H20" r:id="rId124" xr:uid="{00000000-0004-0000-0200-00007B000000}"/>
+    <hyperlink ref="I20" r:id="rId125" xr:uid="{00000000-0004-0000-0200-00007C000000}"/>
+    <hyperlink ref="J20" r:id="rId126" xr:uid="{00000000-0004-0000-0200-00007D000000}"/>
+    <hyperlink ref="E21" r:id="rId127" xr:uid="{00000000-0004-0000-0200-00007E000000}"/>
+    <hyperlink ref="F21" r:id="rId128" xr:uid="{00000000-0004-0000-0200-00007F000000}"/>
+    <hyperlink ref="G21" r:id="rId129" xr:uid="{00000000-0004-0000-0200-000080000000}"/>
+    <hyperlink ref="J21" r:id="rId130" xr:uid="{00000000-0004-0000-0200-000081000000}"/>
+    <hyperlink ref="K21" r:id="rId131" xr:uid="{00000000-0004-0000-0200-000082000000}"/>
+    <hyperlink ref="L21" r:id="rId132" xr:uid="{00000000-0004-0000-0200-000083000000}"/>
+    <hyperlink ref="P21" r:id="rId133" xr:uid="{00000000-0004-0000-0200-000084000000}"/>
+    <hyperlink ref="R21" r:id="rId134" xr:uid="{00000000-0004-0000-0200-000085000000}"/>
+    <hyperlink ref="S21" r:id="rId135" xr:uid="{00000000-0004-0000-0200-000086000000}"/>
+    <hyperlink ref="E22" r:id="rId136" xr:uid="{00000000-0004-0000-0200-000087000000}"/>
+    <hyperlink ref="K22" r:id="rId137" xr:uid="{00000000-0004-0000-0200-000088000000}"/>
+    <hyperlink ref="L22" r:id="rId138" xr:uid="{00000000-0004-0000-0200-000089000000}"/>
+    <hyperlink ref="M22" r:id="rId139" xr:uid="{00000000-0004-0000-0200-00008A000000}"/>
+    <hyperlink ref="N22" r:id="rId140" xr:uid="{00000000-0004-0000-0200-00008B000000}"/>
+    <hyperlink ref="O22" r:id="rId141" xr:uid="{00000000-0004-0000-0200-00008C000000}"/>
+    <hyperlink ref="P22" r:id="rId142" xr:uid="{00000000-0004-0000-0200-00008D000000}"/>
+    <hyperlink ref="Q22" r:id="rId143" xr:uid="{00000000-0004-0000-0200-00008E000000}"/>
+    <hyperlink ref="R22" r:id="rId144" xr:uid="{00000000-0004-0000-0200-00008F000000}"/>
+    <hyperlink ref="S22" r:id="rId145" xr:uid="{00000000-0004-0000-0200-000090000000}"/>
+    <hyperlink ref="T22" r:id="rId146" xr:uid="{00000000-0004-0000-0200-000091000000}"/>
+    <hyperlink ref="E23" r:id="rId147" xr:uid="{00000000-0004-0000-0200-000092000000}"/>
+    <hyperlink ref="F23" r:id="rId148" xr:uid="{00000000-0004-0000-0200-000093000000}"/>
+    <hyperlink ref="G23" r:id="rId149" xr:uid="{00000000-0004-0000-0200-000094000000}"/>
+    <hyperlink ref="J23" r:id="rId150" xr:uid="{00000000-0004-0000-0200-000095000000}"/>
+    <hyperlink ref="C24" r:id="rId151" xr:uid="{00000000-0004-0000-0200-000096000000}"/>
+    <hyperlink ref="G24" r:id="rId152" xr:uid="{00000000-0004-0000-0200-000097000000}"/>
+    <hyperlink ref="I24" r:id="rId153" xr:uid="{00000000-0004-0000-0200-000098000000}"/>
+    <hyperlink ref="M24" r:id="rId154" xr:uid="{00000000-0004-0000-0200-000099000000}"/>
+    <hyperlink ref="P24" r:id="rId155" xr:uid="{00000000-0004-0000-0200-00009A000000}"/>
+    <hyperlink ref="R24" r:id="rId156" xr:uid="{00000000-0004-0000-0200-00009B000000}"/>
+    <hyperlink ref="S24" r:id="rId157" xr:uid="{00000000-0004-0000-0200-00009C000000}"/>
+    <hyperlink ref="C25" r:id="rId158" xr:uid="{00000000-0004-0000-0200-00009D000000}"/>
+    <hyperlink ref="D25" r:id="rId159" xr:uid="{00000000-0004-0000-0200-00009E000000}"/>
+    <hyperlink ref="E25" r:id="rId160" xr:uid="{00000000-0004-0000-0200-00009F000000}"/>
+    <hyperlink ref="F25" r:id="rId161" xr:uid="{00000000-0004-0000-0200-0000A0000000}"/>
+    <hyperlink ref="G25" r:id="rId162" xr:uid="{00000000-0004-0000-0200-0000A1000000}"/>
+    <hyperlink ref="H25" r:id="rId163" xr:uid="{00000000-0004-0000-0200-0000A2000000}"/>
+    <hyperlink ref="I25" r:id="rId164" xr:uid="{00000000-0004-0000-0200-0000A3000000}"/>
+    <hyperlink ref="J25" r:id="rId165" xr:uid="{00000000-0004-0000-0200-0000A4000000}"/>
+    <hyperlink ref="K25" r:id="rId166" xr:uid="{00000000-0004-0000-0200-0000A5000000}"/>
+    <hyperlink ref="C26" r:id="rId167" xr:uid="{00000000-0004-0000-0200-0000A6000000}"/>
+    <hyperlink ref="D26" r:id="rId168" xr:uid="{00000000-0004-0000-0200-0000A7000000}"/>
+    <hyperlink ref="F26" r:id="rId169" xr:uid="{00000000-0004-0000-0200-0000A8000000}"/>
+    <hyperlink ref="G26" r:id="rId170" xr:uid="{00000000-0004-0000-0200-0000A9000000}"/>
+    <hyperlink ref="I26" r:id="rId171" xr:uid="{00000000-0004-0000-0200-0000AA000000}"/>
+    <hyperlink ref="J26" r:id="rId172" xr:uid="{00000000-0004-0000-0200-0000AB000000}"/>
+    <hyperlink ref="L26" r:id="rId173" xr:uid="{00000000-0004-0000-0200-0000AC000000}"/>
+    <hyperlink ref="M26" r:id="rId174" xr:uid="{00000000-0004-0000-0200-0000AD000000}"/>
+    <hyperlink ref="O26" r:id="rId175" xr:uid="{00000000-0004-0000-0200-0000AE000000}"/>
+    <hyperlink ref="Q26" r:id="rId176" xr:uid="{00000000-0004-0000-0200-0000AF000000}"/>
+    <hyperlink ref="S26" r:id="rId177" xr:uid="{00000000-0004-0000-0200-0000B0000000}"/>
+    <hyperlink ref="C27" r:id="rId178" xr:uid="{00000000-0004-0000-0200-0000B1000000}"/>
+    <hyperlink ref="D27" r:id="rId179" xr:uid="{00000000-0004-0000-0200-0000B2000000}"/>
+    <hyperlink ref="E27" r:id="rId180" xr:uid="{00000000-0004-0000-0200-0000B3000000}"/>
+    <hyperlink ref="F27" r:id="rId181" xr:uid="{00000000-0004-0000-0200-0000B4000000}"/>
+    <hyperlink ref="G27" r:id="rId182" xr:uid="{00000000-0004-0000-0200-0000B5000000}"/>
+    <hyperlink ref="H27" r:id="rId183" xr:uid="{00000000-0004-0000-0200-0000B6000000}"/>
+    <hyperlink ref="I27" r:id="rId184" xr:uid="{00000000-0004-0000-0200-0000B7000000}"/>
+    <hyperlink ref="J27" r:id="rId185" xr:uid="{00000000-0004-0000-0200-0000B8000000}"/>
+    <hyperlink ref="K27" r:id="rId186" xr:uid="{00000000-0004-0000-0200-0000B9000000}"/>
+    <hyperlink ref="L27" r:id="rId187" xr:uid="{00000000-0004-0000-0200-0000BA000000}"/>
+    <hyperlink ref="M27" r:id="rId188" xr:uid="{00000000-0004-0000-0200-0000BB000000}"/>
+    <hyperlink ref="N27" r:id="rId189" xr:uid="{00000000-0004-0000-0200-0000BC000000}"/>
+    <hyperlink ref="O27" r:id="rId190" xr:uid="{00000000-0004-0000-0200-0000BD000000}"/>
+    <hyperlink ref="P27" r:id="rId191" xr:uid="{00000000-0004-0000-0200-0000BE000000}"/>
+    <hyperlink ref="Q27" r:id="rId192" xr:uid="{00000000-0004-0000-0200-0000BF000000}"/>
+    <hyperlink ref="R27" r:id="rId193" xr:uid="{00000000-0004-0000-0200-0000C0000000}"/>
+    <hyperlink ref="S27" r:id="rId194" xr:uid="{00000000-0004-0000-0200-0000C1000000}"/>
+    <hyperlink ref="T27" r:id="rId195" xr:uid="{00000000-0004-0000-0200-0000C2000000}"/>
+    <hyperlink ref="C28" r:id="rId196" xr:uid="{00000000-0004-0000-0200-0000C3000000}"/>
+    <hyperlink ref="D28" r:id="rId197" xr:uid="{00000000-0004-0000-0200-0000C4000000}"/>
+    <hyperlink ref="E28" r:id="rId198" xr:uid="{00000000-0004-0000-0200-0000C5000000}"/>
+    <hyperlink ref="F28" r:id="rId199" xr:uid="{00000000-0004-0000-0200-0000C6000000}"/>
+    <hyperlink ref="L28" r:id="rId200" xr:uid="{00000000-0004-0000-0200-0000C7000000}"/>
+    <hyperlink ref="M28" r:id="rId201" xr:uid="{00000000-0004-0000-0200-0000C8000000}"/>
+    <hyperlink ref="N28" r:id="rId202" xr:uid="{00000000-0004-0000-0200-0000C9000000}"/>
+    <hyperlink ref="P28" r:id="rId203" xr:uid="{00000000-0004-0000-0200-0000CA000000}"/>
+    <hyperlink ref="Q28" r:id="rId204" xr:uid="{00000000-0004-0000-0200-0000CB000000}"/>
+    <hyperlink ref="R28" r:id="rId205" xr:uid="{00000000-0004-0000-0200-0000CC000000}"/>
+    <hyperlink ref="S28" r:id="rId206" xr:uid="{00000000-0004-0000-0200-0000CD000000}"/>
+    <hyperlink ref="T28" r:id="rId207" xr:uid="{00000000-0004-0000-0200-0000CE000000}"/>
+    <hyperlink ref="S29" r:id="rId208" xr:uid="{00000000-0004-0000-0200-0000CF000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/02-data/02-gt-artifacts.xlsx
+++ b/02-data/02-gt-artifacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liuxiaoran/Downloads/icsa-2025-replication-package/02-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A8DA2A-FF84-8440-8B8F-04945F3F4F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BC0C39-6A77-724F-A917-C1D24A9B918D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="646">
   <si>
     <t>Components</t>
   </si>
@@ -1259,62 +1259,6 @@
   <si>
     <t>Stella Atari 2600 Emulator
 src/emucore/ and src/common/</t>
-  </si>
-  <si>
-    <t>Domain Model</t>
-  </si>
-  <si>
-    <t>the abstract representation of the problem domain about entities, 
-their attributes, relationships, and rules.
-(import the files, not the component!)</t>
-  </si>
-  <si>
-    <t>In each env package: e.g., classic_control problem 
-definitions, toy_text MDPs, box2d world setup; 
-Atari ROMs via ALE (external).</t>
-  </si>
-  <si>
-    <t>In each env package; e.g., pettingzoo.mpe 
-scenarios, pettingzoo.classic rules, 
-pettingzoo.atari ROM-tied specs</t>
-  </si>
-  <si>
-    <t>Unity Scene: GameObjects, custom scripts with task rules.
-(user scripts to custom domain model)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">implemented in the subclass
-asset (load_asset)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> importing OBJ, FBX, and glTF formats.
-also can add some materials</t>
-  </si>
-  <si>
-    <t>mjcf/: mjcf_model
-suite/: the domains and tasks (A domain refers to a physical model, 
-while a task refers to an instance of that model with a particular 
-MDP structure. For example the difference between the swingup 
-and balance tasks of the cartpole domain is whether the pole is 
-initialised pointing downwards or upwards, respectively.)
-locomotion/: facilitates the creation of environments that require 
-walkers to perform a task in an arena.
-walkers: detached bodies that can move around in the environment.
-arenas: the surroundings in which the walkers and possibly 
-other objects exist.
-tasks: the specification of observations and rewards that are 
-passed from the "environment" to the "agent", along with runtime 
-details such as initialization and termination logic.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.map files  (Level geometry) + 
-game_scripts/levels/*.lua (Level definitions) </t>
-  </si>
-  <si>
-    <t>ROMs: Game logic encoded in Atari 2600 ROM files
-(each game has its own domain model encoded in ROM)
-ale_py.roms module handles ROM files</t>
   </si>
   <si>
     <t>Stats Recorder</t>
@@ -3376,10 +3320,6 @@
     <t>simulate</t>
   </si>
   <si>
-    <t>Executes simulation, provides low-level step primitives.
-has model in it</t>
-  </si>
-  <si>
     <t>Data / Persistence</t>
   </si>
   <si>
@@ -7735,6 +7675,228 @@
     The API is inspired by [brax](https://github.com/google/brax/blob/main/brax/envs/env.py).
     """</t>
     </r>
+  </si>
+  <si>
+    <t>Action: each env’s step() to execute;</t>
+  </si>
+  <si>
+    <t>Action: In each env’s step() to execute;</t>
+  </si>
+  <si>
+    <t>def set_actions(self, behavior_name: BehaviorName, action: ActionTuple) -&gt; None:
+        """
+        Sets the action for all of the agents in the simulation for the next
+        step. The Actions must be in the same order as the order received in
+        the DecisionSteps.</t>
+  </si>
+  <si>
+    <t>Action: 
+Action Processing Pipeline (in step()):</t>
+  </si>
+  <si>
+    <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab/isaaclab/managers/action_manager.py 
+isaaclab.managers/ActionManager
+Action Manager: The action manager that processes the raw actions sent to the environment and converts them to low-level commands that are sent to the simulation. It can be configured to accept raw actions at different levels of abstraction. For example, in case of a robotic arm, the raw actions can be joint torques, joint positions, or end-effector poses. Similarly for a mobile base, it can be  the joint torques, or the desired velocity of the floating base.</t>
+  </si>
+  <si>
+    <t>Action: rl/control.py: inside step()
+task.before_step(self, action, physics): 
+Updates the task from the provided action.
+rl/control.py: inside step()
+task.before_step(self, action, physics): 
+Updates the task from the provided action.
+composer/task.py: 
+- action_spec(self, physics) (Defines action space bounds)
+Returns a `BoundedArray` spec matching the `Physics` actuators.
+- before_step(self, action, physics)</t>
+  </si>
+  <si>
+    <t>inside step(self, action)
+customDiscreteActionSpec is called after init, 
+it returns an additional array of extra actions supplied by the script.</t>
+  </si>
+  <si>
+    <t>in step()
+act(Action a)
+reward_t ALEInterface::act(Action action, float paddle_strength)
+Applies an action to the game and returns the reward.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">in step(self, state: State, action: chex.Array) -&gt; Tuple[State, TimeStep[Observation]]:
+    """Run one timestep of the environment's dynamics."""
+For example, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/instadeepai/jumanji/blob/main/jumanji/environments/routing/pac_man/env.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  
+def step(self, state, action):
+    updated_state, collision_rewards = self._update_state(state, action)
+def _update_state(self, state: State, action: chex.Array) -&gt; Tuple[State, int]:
+        """Updates the state of the environment.</t>
+    </r>
+  </si>
+  <si>
+    <t>Observation: step() reset() return observation value</t>
+  </si>
+  <si>
+    <t>Observation: Inside each env’s observe(agent) method (AEC) 
+or in its step() return (Parallel)</t>
+  </si>
+  <si>
+    <t>rl_output = outputs.rl_output
+self._update_state(rl_output)
+https://github.com/Unity-Technologies/ml-agents/blob/develop/ml-agents-envs/mlagents_envs/environment.py#L332
+ public enum ObservationType
+    {
+        /// &lt;summary&gt;
+        /// Collected observations are generic.
+    public interface ISensor
+    {
+        /// &lt;summary&gt;
+        /// Returns a description of the observations that will be generated by the sensor.
+        /// &lt;/summary&gt;
+        /// &lt;returns&gt;An object describing the observation.&lt;/returns&gt;
+        ObservationSpec GetObservationSpec();
+https://github.com/Unity-Technologies/ml-agents/blob/develop/ml-agents-envs/mlagents_envs/base_env.py 
+class ObservationSpec(NamedTuple):
+    """
+    A NamedTuple containing information about the observation of Agents.</t>
+  </si>
+  <si>
+    <t>observation+reward: in post_physics_step(); self.rew_buf; return in step()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observation Manager
+Manager for computing observation signals for a given world.
+https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab/isaaclab/managers/reward_manager.py </t>
+  </si>
+  <si>
+    <t>Obs:rl/control.py: get_observation(self, physics): 
+Returns an observation from the environment;
+rl/control.py: get_observation(self, physics): 
+Returns an observation from the environment;
+composer/observation/observable: Observable (e.g. MujocoCamera)
+get_observation()/observation_callable(physics): where/how to call?
+entity + observables -&gt; multi entity + task -&gt; composer?</t>
+  </si>
+  <si>
+    <t>inside step(self, action)
+customObservationSpec() → array
+Called after init, it returns an additional array of extra observation 
+types supplied by the script.
+customObservation(name) → tensor.ByteTensor or tensor.DoubleTensor.
+return a tensor of a matching shape and type as specified in 
+customObservationSpec</t>
+  </si>
+  <si>
+    <t>in step()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in step(self, state: State, action: chex.Array) -&gt; Tuple[State, TimeStep[Observation]]:
+    """Run one timestep of the environment's dynamics."""
+For example, https://github.com/instadeepai/jumanji/blob/main/jumanji/environments/routing/pac_man/env.py 
+def _observation_from_state(self, state: State) -&gt; Observation:
+        """Create an observation from the state of the environment."""
+</t>
+  </si>
+  <si>
+    <t>Reward: calculated inside each env’s step()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward: Inside each env’s step()
+internally, the env keeps a per-agent 
+env.rewards[agent] dict that accumulates 
+increments between that agent’s turn
+env.last() method provides cumulative rewards 
+since agent's last action for current agent </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inside each env's step()
+def get_steps(
+        self, behavior_name: BehaviorName
+    ) -&gt; Tuple[DecisionSteps, TerminalSteps]:
+        """
+        Retrieves the steps of the agents that requested a step in the
+        simulation.
+        :param behavior_name: The name of the behavior the agents are part of
+        :return: A tuple containing :
+         - A DecisionSteps NamedTuple containing the observations,
+         the rewards, the agent ids and the action masks for the Agents
+         of the specified behavior. These Agents need an action this step.
+         - A TerminalSteps NamedTuple containing the observations,
+         rewards, agent ids and interrupted flags of the agents that had their
+         episode terminated last step.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://github.com/isaac-sim/IsaacLab/blob/main/source/isaaclab/isaaclab/managers/reward_manager.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Reward Manager
+Manager for computing reward signals for a given world.</t>
+    </r>
+  </si>
+  <si>
+    <t>Reward:rl/control.py: get_reward(self, physics):
+Returns a reward from the environment.
+rl/control.py: get_reward(self, physics):
+Returns a reward from the environment.
+composer/task.py: get_reward(self, physics):
+Calculates the reward signal given the physics state.
+dm_control/utils/rewards.py: reward shaping utilities (e.g. sigmoids)</t>
+  </si>
+  <si>
+    <t>inside step(self, action)
+api:reward()
+computed in level Lua (“gameplay logic”), not in Python. 
+Designers specify when to send positive/negative reward
+and the engine forwards the scalar to Python in step() results.</t>
+  </si>
+  <si>
+    <t>in step()
+reward += self.ale.act(action_idx, strength)
+Base rewards: Game score changes detected from Stella simulator
+(return by act())</t>
+  </si>
+  <si>
+    <t>in step(self, state: State, action: chex.Array) -&gt; Tuple[State, TimeStep[Observation]]:
+    """Run one timestep of the environment's dynamics."""
+For example, https://github.com/instadeepai/jumanji/blob/main/jumanji/environments/routing/pac_man/env.py 
+def _update_state(self, state, action):
+...
+reward = collision_rewards + power_up_rewards + ghost_col_rewards
+        state.score = jnp.array(state.score + reward, jnp.int32)
+        return state, reward</t>
   </si>
   <si>
     <r>
@@ -12017,10 +12179,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12256,18 +12418,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH1005"/>
+  <dimension ref="A1:AH1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="35.1640625" customWidth="1"/>
+    <col min="5" max="5" width="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="45.6640625" customWidth="1"/>
     <col min="7" max="7" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="50.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="50.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="53.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="49.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="50.5" customWidth="1"/>
@@ -12942,33 +13104,33 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:21" ht="306" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:21" ht="332" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>159</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="4" t="s">
         <v>162</v>
       </c>
+      <c r="E13" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="F13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>167</v>
@@ -12976,17 +13138,15 @@
       <c r="K13" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -12995,142 +13155,136 @@
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="1:21" ht="332" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>171</v>
+        <v>160</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="L14" s="4"/>
+        <v>181</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>182</v>
+      </c>
       <c r="M14" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="T14" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="U14" s="4"/>
     </row>
     <row r="15" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>187</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="J15" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="M15" s="4"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="S15" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="T15" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="6"/>
+        <v>195</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>200</v>
-      </c>
+      <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="4"/>
+      <c r="M16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q16" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
       <c r="R16" s="4" t="s">
         <v>202</v>
       </c>
@@ -13140,29 +13294,29 @@
       <c r="T16" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="U16" s="4"/>
-    </row>
-    <row r="17" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="U16" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" ht="98" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>207</v>
-      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>208</v>
@@ -13182,10 +13336,10 @@
       <c r="S17" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="T17" s="4" t="s">
+      <c r="T17" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="U17" s="4" t="s">
+      <c r="U17" s="5" t="s">
         <v>215</v>
       </c>
     </row>
@@ -13199,179 +13353,181 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="N18" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="O18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="P18" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" ht="98" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>196</v>
+      </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>221</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
+      <c r="M19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>223</v>
+      </c>
       <c r="Q19" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R19" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+    </row>
+    <row r="20" spans="1:34" ht="306" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="S19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A20" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="4" t="s">
-        <v>230</v>
-      </c>
+      <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
+      <c r="L20" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="M20" s="4" t="s">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-    </row>
-    <row r="21" spans="1:34" ht="306" x14ac:dyDescent="0.15">
+        <v>237</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" ht="280" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="4" t="s">
-        <v>239</v>
-      </c>
+      <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
-        <v>240</v>
-      </c>
+      <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="22" spans="1:34" ht="280" x14ac:dyDescent="0.15">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -13383,303 +13539,277 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="O22" s="5" t="s">
         <v>255</v>
       </c>
+      <c r="O22" s="4" t="s">
+        <v>256</v>
+      </c>
       <c r="P22" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q22" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="Q22" s="2" t="s">
         <v>258</v>
       </c>
+      <c r="R22" s="10" t="s">
+        <v>259</v>
+      </c>
       <c r="S22" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" ht="182" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>264</v>
+        <v>61</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="R23" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q23" s="4" t="s">
         <v>269</v>
       </c>
+      <c r="R23" s="4" t="s">
+        <v>270</v>
+      </c>
       <c r="S23" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="T23" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+    </row>
+    <row r="24" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A24" s="4" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="24" spans="1:34" ht="182" x14ac:dyDescent="0.15">
-      <c r="A24" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>275</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
+      <c r="L24" s="4" t="s">
+        <v>276</v>
+      </c>
       <c r="M24" s="4" t="s">
-        <v>61</v>
+        <v>277</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>61</v>
+        <v>280</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
+        <v>283</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="25" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>284</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>288</v>
+      </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q25" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>292</v>
+      <c r="R25" s="5" t="s">
+        <v>294</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="26" spans="1:34" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A26" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="F26" s="4" t="s">
+    </row>
+    <row r="26" spans="1:34" ht="168" x14ac:dyDescent="0.15">
+      <c r="A26" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
+      <c r="B26" s="8"/>
+      <c r="C26" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="M26" s="4" t="s">
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="12"/>
+      <c r="AB26" s="12"/>
+      <c r="AC26" s="12"/>
+      <c r="AD26" s="12"/>
+      <c r="AE26" s="12"/>
+      <c r="AF26" s="12"/>
+      <c r="AG26" s="12"/>
+      <c r="AH26" s="12"/>
+    </row>
+    <row r="27" spans="1:34" ht="345" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="R27" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="P26" s="4" t="s">
+      <c r="S27" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="Q26" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="R26" s="5" t="s">
+      <c r="T27" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="S26" s="4" t="s">
+      <c r="U27" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="T26" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="27" spans="1:34" ht="168" x14ac:dyDescent="0.15">
-      <c r="A27" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
-      <c r="AC27" s="12"/>
-      <c r="AD27" s="12"/>
-      <c r="AE27" s="12"/>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="12"/>
-    </row>
-    <row r="28" spans="1:34" ht="345" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="R28" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="S28" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="T28" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>315</v>
-      </c>
+    </row>
+    <row r="28" spans="1:34" ht="13" x14ac:dyDescent="0.15">
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
     </row>
     <row r="29" spans="1:34" ht="13" x14ac:dyDescent="0.15">
+      <c r="A29" s="14"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
@@ -13691,7 +13821,7 @@
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
-      <c r="O29" s="14"/>
+      <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
@@ -13721,7 +13851,6 @@
       <c r="U30" s="13"/>
     </row>
     <row r="31" spans="1:34" ht="13" x14ac:dyDescent="0.15">
-      <c r="A31" s="14"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -33201,26 +33330,6 @@
       <c r="T1004" s="13"/>
       <c r="U1004" s="13"/>
     </row>
-    <row r="1005" spans="4:21" ht="13" x14ac:dyDescent="0.15">
-      <c r="D1005" s="13"/>
-      <c r="E1005" s="13"/>
-      <c r="F1005" s="13"/>
-      <c r="G1005" s="13"/>
-      <c r="H1005" s="13"/>
-      <c r="I1005" s="13"/>
-      <c r="J1005" s="13"/>
-      <c r="K1005" s="13"/>
-      <c r="L1005" s="13"/>
-      <c r="M1005" s="13"/>
-      <c r="N1005" s="13"/>
-      <c r="O1005" s="13"/>
-      <c r="P1005" s="13"/>
-      <c r="Q1005" s="13"/>
-      <c r="R1005" s="13"/>
-      <c r="S1005" s="13"/>
-      <c r="T1005" s="13"/>
-      <c r="U1005" s="13"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -33230,9 +33339,9 @@
     <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="D8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="D10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="U18" r:id="rId8" location="tianshou/config.py" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O22" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="R26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="U17" r:id="rId8" location="tianshou/config.py" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="R25" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33256,48 +33365,48 @@
   <sheetData>
     <row r="1" spans="1:27" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:27" ht="42" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:27" ht="28" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -33306,63 +33415,63 @@
     </row>
     <row r="4" spans="1:27" ht="98" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:27" ht="28" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:27" ht="154" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:27" ht="84" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="16"/>
@@ -33389,17 +33498,17 @@
     </row>
     <row r="8" spans="1:27" ht="126" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="16"/>
@@ -33426,84 +33535,84 @@
     </row>
     <row r="9" spans="1:27" ht="56" x14ac:dyDescent="0.15">
       <c r="A9" s="33" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="28" x14ac:dyDescent="0.15">
       <c r="A10" s="34"/>
       <c r="B10" s="4" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="70" x14ac:dyDescent="0.15">
       <c r="A11" s="34"/>
       <c r="B11" s="4" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="56" x14ac:dyDescent="0.15">
       <c r="A12" s="35"/>
-      <c r="B12" s="4" t="s">
-        <v>345</v>
+      <c r="B12" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>346</v>
+      <c r="E12" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:27" ht="42" x14ac:dyDescent="0.15">
       <c r="A13" s="33" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="28" x14ac:dyDescent="0.15">
@@ -33511,13 +33620,13 @@
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
       <c r="D14" s="4" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="28" x14ac:dyDescent="0.15">
@@ -33525,13 +33634,13 @@
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="4" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="42" x14ac:dyDescent="0.15">
@@ -33542,7 +33651,7 @@
         <v>142</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="12"/>
@@ -33575,10 +33684,10 @@
         <v>117</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="42" x14ac:dyDescent="0.15">
@@ -33587,16 +33696,16 @@
         <v>129</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.15">
@@ -33604,122 +33713,122 @@
       <c r="B19" s="35"/>
       <c r="C19" s="35"/>
       <c r="D19" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.15">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="35"/>
       <c r="B20" s="4" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>369</v>
+        <v>150</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" ht="112" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="42" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="42" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" ht="56" x14ac:dyDescent="0.15">
       <c r="A25" s="15" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="15" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A26" s="15" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="F26" s="4"/>
     </row>
@@ -33741,7 +33850,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -33751,7 +33860,7 @@
     <col min="5" max="5" width="56.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5" customWidth="1"/>
     <col min="9" max="9" width="34.83203125" customWidth="1"/>
     <col min="10" max="10" width="32.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="31.83203125" bestFit="1" customWidth="1"/>
@@ -33768,61 +33877,61 @@
     <row r="1" spans="1:21" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="17"/>
       <c r="B1" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="S1" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="T1" s="36" t="s">
         <v>387</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="M1" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q1" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="R1" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="S1" s="18" t="s">
-        <v>397</v>
-      </c>
-      <c r="T1" s="36" t="s">
-        <v>398</v>
       </c>
       <c r="U1" s="37"/>
     </row>
@@ -33886,10 +33995,10 @@
     </row>
     <row r="3" spans="1:21" ht="28" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>21</v>
@@ -33948,7 +34057,7 @@
     </row>
     <row r="4" spans="1:21" ht="384" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="20"/>
@@ -33962,7 +34071,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="21" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -33974,15 +34083,15 @@
     </row>
     <row r="5" spans="1:21" ht="397" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="21" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
@@ -33991,39 +34100,39 @@
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="L5" s="21" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="N5" s="21" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="P5" s="21" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="R5" s="21" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="S5" s="21" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="T5" s="22" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="345" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -34036,14 +34145,14 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="23" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="N6" s="23" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="O6" s="20"/>
       <c r="P6" s="23" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
@@ -34052,10 +34161,10 @@
     </row>
     <row r="7" spans="1:21" ht="70" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -34072,7 +34181,7 @@
       <c r="O7" s="20"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="22" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="R7" s="20"/>
       <c r="S7" s="20"/>
@@ -34080,13 +34189,13 @@
     </row>
     <row r="8" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
       <c r="E8" s="21" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -34095,44 +34204,44 @@
       <c r="J8" s="20"/>
       <c r="K8" s="20"/>
       <c r="L8" s="21" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="N8" s="21" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="Q8" s="21" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="R8" s="21" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="T8" s="22" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
       <c r="E9" s="22" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -34141,46 +34250,46 @@
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
       <c r="L9" s="21" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P9" s="24" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="Q9" s="21" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="R9" s="21" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="T9" s="21" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
       <c r="G10" s="23" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
@@ -34189,42 +34298,42 @@
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
       <c r="N10" s="22" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="O10" s="20"/>
       <c r="P10" s="24" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="T10" s="22" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="21" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="21" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
@@ -34233,27 +34342,27 @@
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
       <c r="N11" s="21" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="26" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="Q11" s="21" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
       <c r="T11" s="21" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -34267,30 +34376,30 @@
       <c r="L12" s="20"/>
       <c r="M12" s="20"/>
       <c r="N12" s="23" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="Q12" s="20"/>
       <c r="R12" s="21" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
     </row>
     <row r="13" spans="1:21" ht="224" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
       <c r="E13" s="22" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
@@ -34299,44 +34408,44 @@
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
       <c r="L13" s="22" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="M13" s="24" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="N13" s="22" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="P13" s="24" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="R13" s="22" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="S13" s="22" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="T13" s="22" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="306" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="22" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
@@ -34345,44 +34454,44 @@
       <c r="J14" s="20"/>
       <c r="K14" s="20"/>
       <c r="L14" s="22" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="N14" s="22" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P14" s="24" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="R14" s="21" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="S14" s="21" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="T14" s="22" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="22" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
@@ -34391,44 +34500,44 @@
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
       <c r="L15" s="22" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="M15" s="24" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="N15" s="22" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="P15" s="24" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="R15" s="23" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="S15" s="22" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="T15" s="22" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
       <c r="E16" s="21" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
@@ -34437,64 +34546,64 @@
       <c r="J16" s="20"/>
       <c r="K16" s="20"/>
       <c r="L16" s="21" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="M16" s="24" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="N16" s="22" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="O16" s="22" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="P16" s="24" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="Q16" s="26" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="R16" s="21" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="S16" s="21" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="T16" s="22" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="358" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="22" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="L17" s="20"/>
       <c r="M17" s="20"/>
@@ -34508,37 +34617,37 @@
     </row>
     <row r="18" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="L18" s="20"/>
       <c r="M18" s="20"/>
@@ -34550,39 +34659,39 @@
       <c r="S18" s="20"/>
       <c r="T18" s="20"/>
     </row>
-    <row r="19" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:20" ht="358" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>347</v>
+        <v>492</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>514</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>515</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>516</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>517</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>518</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>519</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>520</v>
+        <v>86</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>505</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>509</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
@@ -34594,38 +34703,40 @@
       <c r="S19" s="20"/>
       <c r="T19" s="20"/>
     </row>
-    <row r="20" spans="1:20" ht="371" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
-        <v>347</v>
+        <v>492</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>522</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>524</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>526</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>528</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="K20" s="20"/>
+        <v>98</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>511</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>512</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>514</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>517</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>519</v>
+      </c>
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -34636,130 +34747,124 @@
       <c r="S20" s="20"/>
       <c r="T20" s="20"/>
     </row>
-    <row r="21" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:20" ht="358" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>530</v>
+        <v>492</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="27" t="s">
-        <v>531</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>532</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>533</v>
-      </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>536</v>
-      </c>
-      <c r="M21" s="28" t="s">
-        <v>537</v>
-      </c>
-      <c r="N21" s="28" t="s">
-        <v>538</v>
-      </c>
-      <c r="O21" s="28" t="s">
-        <v>539</v>
-      </c>
-      <c r="P21" s="23" t="s">
-        <v>540</v>
-      </c>
-      <c r="Q21" s="28" t="s">
-        <v>541</v>
-      </c>
-      <c r="R21" s="22" t="s">
-        <v>542</v>
-      </c>
-      <c r="S21" s="22" t="s">
-        <v>543</v>
-      </c>
-      <c r="T21" s="28" t="s">
-        <v>544</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>520</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>521</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>514</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>526</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
     </row>
     <row r="22" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>530</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="22" t="s">
-        <v>545</v>
-      </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
+      <c r="F22" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>535</v>
+      </c>
       <c r="K22" s="21" t="s">
-        <v>546</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>547</v>
-      </c>
-      <c r="M22" s="22" t="s">
-        <v>548</v>
-      </c>
-      <c r="N22" s="22" t="s">
-        <v>549</v>
-      </c>
-      <c r="O22" s="22" t="s">
-        <v>550</v>
-      </c>
-      <c r="P22" s="23" t="s">
-        <v>551</v>
-      </c>
-      <c r="Q22" s="22" t="s">
-        <v>552</v>
-      </c>
-      <c r="R22" s="23" t="s">
-        <v>553</v>
-      </c>
-      <c r="S22" s="22" t="s">
-        <v>554</v>
-      </c>
-      <c r="T22" s="22" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+        <v>536</v>
+      </c>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+    </row>
+    <row r="23" spans="1:20" ht="371" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>530</v>
+        <v>337</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
+        <v>129</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>537</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>538</v>
+      </c>
       <c r="E23" s="22" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>557</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>558</v>
-      </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+        <v>540</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>543</v>
+      </c>
       <c r="J23" s="21" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
@@ -34772,279 +34877,415 @@
       <c r="S23" s="20"/>
       <c r="T23" s="20"/>
     </row>
-    <row r="24" spans="1:20" ht="306" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>561</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>562</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
       <c r="E24" s="28" t="s">
-        <v>563</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>564</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>565</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>566</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>567</v>
-      </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="28" t="s">
-        <v>568</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>569</v>
-      </c>
-      <c r="M24" s="30" t="s">
-        <v>570</v>
-      </c>
-      <c r="N24" s="28" t="s">
-        <v>571</v>
-      </c>
-      <c r="O24" s="28" t="s">
-        <v>572</v>
+        <v>546</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>547</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="21" t="s">
+        <v>549</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>550</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="M24" s="27" t="s">
+        <v>552</v>
+      </c>
+      <c r="N24" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="O24" s="27" t="s">
+        <v>554</v>
       </c>
       <c r="P24" s="23" t="s">
-        <v>573</v>
-      </c>
-      <c r="Q24" s="28" t="s">
-        <v>574</v>
+        <v>555</v>
+      </c>
+      <c r="Q24" s="27" t="s">
+        <v>556</v>
       </c>
       <c r="R24" s="22" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>576</v>
-      </c>
-      <c r="T24" s="28" t="s">
-        <v>577</v>
+        <v>558</v>
+      </c>
+      <c r="T24" s="27" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="22" t="s">
         <v>560</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>562</v>
+      </c>
+      <c r="M25" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="N25" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="O25" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="P25" s="23" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q25" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>568</v>
+      </c>
+      <c r="S25" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="T25" s="22" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="22" t="s">
+        <v>571</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+    </row>
+    <row r="27" spans="1:20" ht="306" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="E27" s="27" t="s">
         <v>578</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="F27" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="G27" s="22" t="s">
         <v>580</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="H27" s="27" t="s">
         <v>581</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="I27" s="22" t="s">
         <v>582</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="J27" s="4"/>
+      <c r="K27" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="L27" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="I25" s="22" t="s">
+      <c r="M27" s="30" t="s">
         <v>585</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="N27" s="27" t="s">
         <v>586</v>
       </c>
-      <c r="K25" s="22" t="s">
+      <c r="O27" s="27" t="s">
         <v>587</v>
       </c>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-    </row>
-    <row r="26" spans="1:20" ht="371" x14ac:dyDescent="0.15">
-      <c r="A26" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C26" s="22" t="s">
+      <c r="P27" s="23" t="s">
         <v>588</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="Q27" s="27" t="s">
         <v>589</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="21" t="s">
+      <c r="R27" s="22" t="s">
         <v>590</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="S27" s="22" t="s">
         <v>591</v>
       </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="22" t="s">
+      <c r="T27" s="27" t="s">
         <v>592</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>593</v>
-      </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="22" t="s">
-        <v>594</v>
-      </c>
-      <c r="M26" s="22" t="s">
-        <v>595</v>
-      </c>
-      <c r="N26" s="20"/>
-      <c r="O26" s="22" t="s">
-        <v>596</v>
-      </c>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="21" t="s">
-        <v>597</v>
-      </c>
-      <c r="R26" s="20"/>
-      <c r="S26" s="22" t="s">
-        <v>598</v>
-      </c>
-      <c r="T26" s="20"/>
-    </row>
-    <row r="27" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>599</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>600</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>602</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>606</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>608</v>
-      </c>
-      <c r="M27" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="N27" s="22" t="s">
-        <v>610</v>
-      </c>
-      <c r="O27" s="22" t="s">
-        <v>611</v>
-      </c>
-      <c r="P27" s="23" t="s">
-        <v>612</v>
-      </c>
-      <c r="Q27" s="23" t="s">
-        <v>613</v>
-      </c>
-      <c r="R27" s="23" t="s">
-        <v>614</v>
-      </c>
-      <c r="S27" s="22" t="s">
-        <v>615</v>
-      </c>
-      <c r="T27" s="23" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>594</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+    </row>
+    <row r="29" spans="1:20" ht="371" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="H29" s="20"/>
+      <c r="I29" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="K29" s="20"/>
+      <c r="L29" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="N29" s="20"/>
+      <c r="O29" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="R29" s="20"/>
+      <c r="S29" s="22" t="s">
+        <v>613</v>
+      </c>
+      <c r="T29" s="20"/>
+    </row>
+    <row r="30" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A30" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>614</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>617</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="G30" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="H30" s="22" t="s">
         <v>619</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="I30" s="22" t="s">
         <v>620</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="J30" s="22" t="s">
         <v>621</v>
       </c>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="23" t="s">
+      <c r="K30" s="22" t="s">
         <v>622</v>
       </c>
-      <c r="M28" s="22" t="s">
+      <c r="L30" s="22" t="s">
         <v>623</v>
       </c>
-      <c r="N28" s="22" t="s">
+      <c r="M30" s="22" t="s">
         <v>624</v>
       </c>
-      <c r="O28" s="20"/>
-      <c r="P28" s="23" t="s">
+      <c r="N30" s="22" t="s">
         <v>625</v>
       </c>
-      <c r="Q28" s="23" t="s">
+      <c r="O30" s="22" t="s">
         <v>626</v>
       </c>
-      <c r="R28" s="23" t="s">
+      <c r="P30" s="23" t="s">
         <v>627</v>
       </c>
-      <c r="S28" s="23" t="s">
+      <c r="Q30" s="23" t="s">
         <v>628</v>
       </c>
-      <c r="T28" s="23" t="s">
+      <c r="R30" s="23" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" ht="13" x14ac:dyDescent="0.15">
-      <c r="S29" s="31" t="s">
+      <c r="S30" s="22" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" ht="98.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" spans="6:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" spans="6:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="F34" s="32"/>
+      <c r="T30" s="23" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A31" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>633</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>634</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>635</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>636</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="23" t="s">
+        <v>637</v>
+      </c>
+      <c r="M31" s="22" t="s">
+        <v>638</v>
+      </c>
+      <c r="N31" s="22" t="s">
+        <v>639</v>
+      </c>
+      <c r="O31" s="20"/>
+      <c r="P31" s="23" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q31" s="23" t="s">
+        <v>641</v>
+      </c>
+      <c r="R31" s="23" t="s">
+        <v>642</v>
+      </c>
+      <c r="S31" s="23" t="s">
+        <v>643</v>
+      </c>
+      <c r="T31" s="23" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="13" x14ac:dyDescent="0.15">
+      <c r="S32" s="31" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" spans="6:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" spans="6:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="F37" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -35160,105 +35401,107 @@
     <hyperlink ref="I18" r:id="rId107" xr:uid="{00000000-0004-0000-0200-00006A000000}"/>
     <hyperlink ref="J18" r:id="rId108" xr:uid="{00000000-0004-0000-0200-00006B000000}"/>
     <hyperlink ref="K18" r:id="rId109" xr:uid="{00000000-0004-0000-0200-00006C000000}"/>
-    <hyperlink ref="C19" r:id="rId110" xr:uid="{00000000-0004-0000-0200-00006D000000}"/>
-    <hyperlink ref="D19" r:id="rId111" xr:uid="{00000000-0004-0000-0200-00006E000000}"/>
-    <hyperlink ref="E19" r:id="rId112" xr:uid="{00000000-0004-0000-0200-00006F000000}"/>
-    <hyperlink ref="F19" r:id="rId113" xr:uid="{00000000-0004-0000-0200-000070000000}"/>
-    <hyperlink ref="G19" r:id="rId114" xr:uid="{00000000-0004-0000-0200-000071000000}"/>
-    <hyperlink ref="H19" r:id="rId115" xr:uid="{00000000-0004-0000-0200-000072000000}"/>
-    <hyperlink ref="I19" r:id="rId116" xr:uid="{00000000-0004-0000-0200-000073000000}"/>
-    <hyperlink ref="J19" r:id="rId117" xr:uid="{00000000-0004-0000-0200-000074000000}"/>
-    <hyperlink ref="K19" r:id="rId118" xr:uid="{00000000-0004-0000-0200-000075000000}"/>
-    <hyperlink ref="C20" r:id="rId119" xr:uid="{00000000-0004-0000-0200-000076000000}"/>
-    <hyperlink ref="D20" r:id="rId120" xr:uid="{00000000-0004-0000-0200-000077000000}"/>
-    <hyperlink ref="E20" r:id="rId121" xr:uid="{00000000-0004-0000-0200-000078000000}"/>
-    <hyperlink ref="F20" r:id="rId122" xr:uid="{00000000-0004-0000-0200-000079000000}"/>
-    <hyperlink ref="G20" r:id="rId123" xr:uid="{00000000-0004-0000-0200-00007A000000}"/>
-    <hyperlink ref="H20" r:id="rId124" xr:uid="{00000000-0004-0000-0200-00007B000000}"/>
-    <hyperlink ref="I20" r:id="rId125" xr:uid="{00000000-0004-0000-0200-00007C000000}"/>
-    <hyperlink ref="J20" r:id="rId126" xr:uid="{00000000-0004-0000-0200-00007D000000}"/>
-    <hyperlink ref="E21" r:id="rId127" xr:uid="{00000000-0004-0000-0200-00007E000000}"/>
-    <hyperlink ref="F21" r:id="rId128" xr:uid="{00000000-0004-0000-0200-00007F000000}"/>
-    <hyperlink ref="G21" r:id="rId129" xr:uid="{00000000-0004-0000-0200-000080000000}"/>
-    <hyperlink ref="J21" r:id="rId130" xr:uid="{00000000-0004-0000-0200-000081000000}"/>
-    <hyperlink ref="K21" r:id="rId131" xr:uid="{00000000-0004-0000-0200-000082000000}"/>
-    <hyperlink ref="L21" r:id="rId132" xr:uid="{00000000-0004-0000-0200-000083000000}"/>
-    <hyperlink ref="P21" r:id="rId133" xr:uid="{00000000-0004-0000-0200-000084000000}"/>
-    <hyperlink ref="R21" r:id="rId134" xr:uid="{00000000-0004-0000-0200-000085000000}"/>
-    <hyperlink ref="S21" r:id="rId135" xr:uid="{00000000-0004-0000-0200-000086000000}"/>
-    <hyperlink ref="E22" r:id="rId136" xr:uid="{00000000-0004-0000-0200-000087000000}"/>
-    <hyperlink ref="K22" r:id="rId137" xr:uid="{00000000-0004-0000-0200-000088000000}"/>
-    <hyperlink ref="L22" r:id="rId138" xr:uid="{00000000-0004-0000-0200-000089000000}"/>
-    <hyperlink ref="M22" r:id="rId139" xr:uid="{00000000-0004-0000-0200-00008A000000}"/>
-    <hyperlink ref="N22" r:id="rId140" xr:uid="{00000000-0004-0000-0200-00008B000000}"/>
-    <hyperlink ref="O22" r:id="rId141" xr:uid="{00000000-0004-0000-0200-00008C000000}"/>
-    <hyperlink ref="P22" r:id="rId142" xr:uid="{00000000-0004-0000-0200-00008D000000}"/>
-    <hyperlink ref="Q22" r:id="rId143" xr:uid="{00000000-0004-0000-0200-00008E000000}"/>
-    <hyperlink ref="R22" r:id="rId144" xr:uid="{00000000-0004-0000-0200-00008F000000}"/>
-    <hyperlink ref="S22" r:id="rId145" xr:uid="{00000000-0004-0000-0200-000090000000}"/>
-    <hyperlink ref="T22" r:id="rId146" xr:uid="{00000000-0004-0000-0200-000091000000}"/>
-    <hyperlink ref="E23" r:id="rId147" xr:uid="{00000000-0004-0000-0200-000092000000}"/>
-    <hyperlink ref="F23" r:id="rId148" xr:uid="{00000000-0004-0000-0200-000093000000}"/>
-    <hyperlink ref="G23" r:id="rId149" xr:uid="{00000000-0004-0000-0200-000094000000}"/>
-    <hyperlink ref="J23" r:id="rId150" xr:uid="{00000000-0004-0000-0200-000095000000}"/>
-    <hyperlink ref="C24" r:id="rId151" xr:uid="{00000000-0004-0000-0200-000096000000}"/>
-    <hyperlink ref="G24" r:id="rId152" xr:uid="{00000000-0004-0000-0200-000097000000}"/>
-    <hyperlink ref="I24" r:id="rId153" xr:uid="{00000000-0004-0000-0200-000098000000}"/>
-    <hyperlink ref="M24" r:id="rId154" xr:uid="{00000000-0004-0000-0200-000099000000}"/>
-    <hyperlink ref="P24" r:id="rId155" xr:uid="{00000000-0004-0000-0200-00009A000000}"/>
-    <hyperlink ref="R24" r:id="rId156" xr:uid="{00000000-0004-0000-0200-00009B000000}"/>
-    <hyperlink ref="S24" r:id="rId157" xr:uid="{00000000-0004-0000-0200-00009C000000}"/>
-    <hyperlink ref="C25" r:id="rId158" xr:uid="{00000000-0004-0000-0200-00009D000000}"/>
-    <hyperlink ref="D25" r:id="rId159" xr:uid="{00000000-0004-0000-0200-00009E000000}"/>
-    <hyperlink ref="E25" r:id="rId160" xr:uid="{00000000-0004-0000-0200-00009F000000}"/>
-    <hyperlink ref="F25" r:id="rId161" xr:uid="{00000000-0004-0000-0200-0000A0000000}"/>
-    <hyperlink ref="G25" r:id="rId162" xr:uid="{00000000-0004-0000-0200-0000A1000000}"/>
-    <hyperlink ref="H25" r:id="rId163" xr:uid="{00000000-0004-0000-0200-0000A2000000}"/>
-    <hyperlink ref="I25" r:id="rId164" xr:uid="{00000000-0004-0000-0200-0000A3000000}"/>
-    <hyperlink ref="J25" r:id="rId165" xr:uid="{00000000-0004-0000-0200-0000A4000000}"/>
-    <hyperlink ref="K25" r:id="rId166" xr:uid="{00000000-0004-0000-0200-0000A5000000}"/>
-    <hyperlink ref="C26" r:id="rId167" xr:uid="{00000000-0004-0000-0200-0000A6000000}"/>
-    <hyperlink ref="D26" r:id="rId168" xr:uid="{00000000-0004-0000-0200-0000A7000000}"/>
-    <hyperlink ref="F26" r:id="rId169" xr:uid="{00000000-0004-0000-0200-0000A8000000}"/>
-    <hyperlink ref="G26" r:id="rId170" xr:uid="{00000000-0004-0000-0200-0000A9000000}"/>
-    <hyperlink ref="I26" r:id="rId171" xr:uid="{00000000-0004-0000-0200-0000AA000000}"/>
-    <hyperlink ref="J26" r:id="rId172" xr:uid="{00000000-0004-0000-0200-0000AB000000}"/>
-    <hyperlink ref="L26" r:id="rId173" xr:uid="{00000000-0004-0000-0200-0000AC000000}"/>
-    <hyperlink ref="M26" r:id="rId174" xr:uid="{00000000-0004-0000-0200-0000AD000000}"/>
-    <hyperlink ref="O26" r:id="rId175" xr:uid="{00000000-0004-0000-0200-0000AE000000}"/>
-    <hyperlink ref="Q26" r:id="rId176" xr:uid="{00000000-0004-0000-0200-0000AF000000}"/>
-    <hyperlink ref="S26" r:id="rId177" xr:uid="{00000000-0004-0000-0200-0000B0000000}"/>
-    <hyperlink ref="C27" r:id="rId178" xr:uid="{00000000-0004-0000-0200-0000B1000000}"/>
-    <hyperlink ref="D27" r:id="rId179" xr:uid="{00000000-0004-0000-0200-0000B2000000}"/>
-    <hyperlink ref="E27" r:id="rId180" xr:uid="{00000000-0004-0000-0200-0000B3000000}"/>
-    <hyperlink ref="F27" r:id="rId181" xr:uid="{00000000-0004-0000-0200-0000B4000000}"/>
-    <hyperlink ref="G27" r:id="rId182" xr:uid="{00000000-0004-0000-0200-0000B5000000}"/>
-    <hyperlink ref="H27" r:id="rId183" xr:uid="{00000000-0004-0000-0200-0000B6000000}"/>
-    <hyperlink ref="I27" r:id="rId184" xr:uid="{00000000-0004-0000-0200-0000B7000000}"/>
-    <hyperlink ref="J27" r:id="rId185" xr:uid="{00000000-0004-0000-0200-0000B8000000}"/>
-    <hyperlink ref="K27" r:id="rId186" xr:uid="{00000000-0004-0000-0200-0000B9000000}"/>
-    <hyperlink ref="L27" r:id="rId187" xr:uid="{00000000-0004-0000-0200-0000BA000000}"/>
-    <hyperlink ref="M27" r:id="rId188" xr:uid="{00000000-0004-0000-0200-0000BB000000}"/>
-    <hyperlink ref="N27" r:id="rId189" xr:uid="{00000000-0004-0000-0200-0000BC000000}"/>
-    <hyperlink ref="O27" r:id="rId190" xr:uid="{00000000-0004-0000-0200-0000BD000000}"/>
-    <hyperlink ref="P27" r:id="rId191" xr:uid="{00000000-0004-0000-0200-0000BE000000}"/>
-    <hyperlink ref="Q27" r:id="rId192" xr:uid="{00000000-0004-0000-0200-0000BF000000}"/>
-    <hyperlink ref="R27" r:id="rId193" xr:uid="{00000000-0004-0000-0200-0000C0000000}"/>
-    <hyperlink ref="S27" r:id="rId194" xr:uid="{00000000-0004-0000-0200-0000C1000000}"/>
-    <hyperlink ref="T27" r:id="rId195" xr:uid="{00000000-0004-0000-0200-0000C2000000}"/>
-    <hyperlink ref="C28" r:id="rId196" xr:uid="{00000000-0004-0000-0200-0000C3000000}"/>
-    <hyperlink ref="D28" r:id="rId197" xr:uid="{00000000-0004-0000-0200-0000C4000000}"/>
-    <hyperlink ref="E28" r:id="rId198" xr:uid="{00000000-0004-0000-0200-0000C5000000}"/>
-    <hyperlink ref="F28" r:id="rId199" xr:uid="{00000000-0004-0000-0200-0000C6000000}"/>
-    <hyperlink ref="L28" r:id="rId200" xr:uid="{00000000-0004-0000-0200-0000C7000000}"/>
-    <hyperlink ref="M28" r:id="rId201" xr:uid="{00000000-0004-0000-0200-0000C8000000}"/>
-    <hyperlink ref="N28" r:id="rId202" xr:uid="{00000000-0004-0000-0200-0000C9000000}"/>
-    <hyperlink ref="P28" r:id="rId203" xr:uid="{00000000-0004-0000-0200-0000CA000000}"/>
-    <hyperlink ref="Q28" r:id="rId204" xr:uid="{00000000-0004-0000-0200-0000CB000000}"/>
-    <hyperlink ref="R28" r:id="rId205" xr:uid="{00000000-0004-0000-0200-0000CC000000}"/>
-    <hyperlink ref="S28" r:id="rId206" xr:uid="{00000000-0004-0000-0200-0000CD000000}"/>
-    <hyperlink ref="T28" r:id="rId207" xr:uid="{00000000-0004-0000-0200-0000CE000000}"/>
-    <hyperlink ref="S29" r:id="rId208" xr:uid="{00000000-0004-0000-0200-0000CF000000}"/>
+    <hyperlink ref="K19" r:id="rId110" xr:uid="{00000000-0004-0000-0200-00006D000000}"/>
+    <hyperlink ref="G21" r:id="rId111" xr:uid="{00000000-0004-0000-0200-00006E000000}"/>
+    <hyperlink ref="C22" r:id="rId112" xr:uid="{00000000-0004-0000-0200-00006F000000}"/>
+    <hyperlink ref="D22" r:id="rId113" xr:uid="{00000000-0004-0000-0200-000070000000}"/>
+    <hyperlink ref="E22" r:id="rId114" xr:uid="{00000000-0004-0000-0200-000071000000}"/>
+    <hyperlink ref="F22" r:id="rId115" xr:uid="{00000000-0004-0000-0200-000072000000}"/>
+    <hyperlink ref="G22" r:id="rId116" xr:uid="{00000000-0004-0000-0200-000073000000}"/>
+    <hyperlink ref="H22" r:id="rId117" xr:uid="{00000000-0004-0000-0200-000074000000}"/>
+    <hyperlink ref="I22" r:id="rId118" xr:uid="{00000000-0004-0000-0200-000075000000}"/>
+    <hyperlink ref="J22" r:id="rId119" xr:uid="{00000000-0004-0000-0200-000076000000}"/>
+    <hyperlink ref="K22" r:id="rId120" xr:uid="{00000000-0004-0000-0200-000077000000}"/>
+    <hyperlink ref="C23" r:id="rId121" xr:uid="{00000000-0004-0000-0200-000078000000}"/>
+    <hyperlink ref="D23" r:id="rId122" xr:uid="{00000000-0004-0000-0200-000079000000}"/>
+    <hyperlink ref="E23" r:id="rId123" xr:uid="{00000000-0004-0000-0200-00007A000000}"/>
+    <hyperlink ref="F23" r:id="rId124" xr:uid="{00000000-0004-0000-0200-00007B000000}"/>
+    <hyperlink ref="G23" r:id="rId125" xr:uid="{00000000-0004-0000-0200-00007C000000}"/>
+    <hyperlink ref="H23" r:id="rId126" xr:uid="{00000000-0004-0000-0200-00007D000000}"/>
+    <hyperlink ref="I23" r:id="rId127" xr:uid="{00000000-0004-0000-0200-00007E000000}"/>
+    <hyperlink ref="J23" r:id="rId128" xr:uid="{00000000-0004-0000-0200-00007F000000}"/>
+    <hyperlink ref="E24" r:id="rId129" xr:uid="{00000000-0004-0000-0200-000080000000}"/>
+    <hyperlink ref="F24" r:id="rId130" xr:uid="{00000000-0004-0000-0200-000081000000}"/>
+    <hyperlink ref="G24" r:id="rId131" xr:uid="{00000000-0004-0000-0200-000082000000}"/>
+    <hyperlink ref="J24" r:id="rId132" xr:uid="{00000000-0004-0000-0200-000083000000}"/>
+    <hyperlink ref="K24" r:id="rId133" xr:uid="{00000000-0004-0000-0200-000084000000}"/>
+    <hyperlink ref="L24" r:id="rId134" xr:uid="{00000000-0004-0000-0200-000085000000}"/>
+    <hyperlink ref="P24" r:id="rId135" xr:uid="{00000000-0004-0000-0200-000086000000}"/>
+    <hyperlink ref="R24" r:id="rId136" xr:uid="{00000000-0004-0000-0200-000087000000}"/>
+    <hyperlink ref="S24" r:id="rId137" xr:uid="{00000000-0004-0000-0200-000088000000}"/>
+    <hyperlink ref="E25" r:id="rId138" xr:uid="{00000000-0004-0000-0200-000089000000}"/>
+    <hyperlink ref="K25" r:id="rId139" xr:uid="{00000000-0004-0000-0200-00008A000000}"/>
+    <hyperlink ref="L25" r:id="rId140" xr:uid="{00000000-0004-0000-0200-00008B000000}"/>
+    <hyperlink ref="M25" r:id="rId141" xr:uid="{00000000-0004-0000-0200-00008C000000}"/>
+    <hyperlink ref="N25" r:id="rId142" xr:uid="{00000000-0004-0000-0200-00008D000000}"/>
+    <hyperlink ref="O25" r:id="rId143" xr:uid="{00000000-0004-0000-0200-00008E000000}"/>
+    <hyperlink ref="P25" r:id="rId144" xr:uid="{00000000-0004-0000-0200-00008F000000}"/>
+    <hyperlink ref="Q25" r:id="rId145" xr:uid="{00000000-0004-0000-0200-000090000000}"/>
+    <hyperlink ref="R25" r:id="rId146" xr:uid="{00000000-0004-0000-0200-000091000000}"/>
+    <hyperlink ref="S25" r:id="rId147" xr:uid="{00000000-0004-0000-0200-000092000000}"/>
+    <hyperlink ref="T25" r:id="rId148" xr:uid="{00000000-0004-0000-0200-000093000000}"/>
+    <hyperlink ref="E26" r:id="rId149" xr:uid="{00000000-0004-0000-0200-000094000000}"/>
+    <hyperlink ref="F26" r:id="rId150" xr:uid="{00000000-0004-0000-0200-000095000000}"/>
+    <hyperlink ref="G26" r:id="rId151" xr:uid="{00000000-0004-0000-0200-000096000000}"/>
+    <hyperlink ref="J26" r:id="rId152" xr:uid="{00000000-0004-0000-0200-000097000000}"/>
+    <hyperlink ref="C27" r:id="rId153" xr:uid="{00000000-0004-0000-0200-000098000000}"/>
+    <hyperlink ref="G27" r:id="rId154" xr:uid="{00000000-0004-0000-0200-000099000000}"/>
+    <hyperlink ref="I27" r:id="rId155" xr:uid="{00000000-0004-0000-0200-00009A000000}"/>
+    <hyperlink ref="M27" r:id="rId156" xr:uid="{00000000-0004-0000-0200-00009B000000}"/>
+    <hyperlink ref="P27" r:id="rId157" xr:uid="{00000000-0004-0000-0200-00009C000000}"/>
+    <hyperlink ref="R27" r:id="rId158" xr:uid="{00000000-0004-0000-0200-00009D000000}"/>
+    <hyperlink ref="S27" r:id="rId159" xr:uid="{00000000-0004-0000-0200-00009E000000}"/>
+    <hyperlink ref="C28" r:id="rId160" xr:uid="{00000000-0004-0000-0200-00009F000000}"/>
+    <hyperlink ref="D28" r:id="rId161" xr:uid="{00000000-0004-0000-0200-0000A0000000}"/>
+    <hyperlink ref="E28" r:id="rId162" xr:uid="{00000000-0004-0000-0200-0000A1000000}"/>
+    <hyperlink ref="F28" r:id="rId163" xr:uid="{00000000-0004-0000-0200-0000A2000000}"/>
+    <hyperlink ref="G28" r:id="rId164" xr:uid="{00000000-0004-0000-0200-0000A3000000}"/>
+    <hyperlink ref="H28" r:id="rId165" xr:uid="{00000000-0004-0000-0200-0000A4000000}"/>
+    <hyperlink ref="I28" r:id="rId166" xr:uid="{00000000-0004-0000-0200-0000A5000000}"/>
+    <hyperlink ref="J28" r:id="rId167" xr:uid="{00000000-0004-0000-0200-0000A6000000}"/>
+    <hyperlink ref="K28" r:id="rId168" xr:uid="{00000000-0004-0000-0200-0000A7000000}"/>
+    <hyperlink ref="C29" r:id="rId169" xr:uid="{00000000-0004-0000-0200-0000A8000000}"/>
+    <hyperlink ref="D29" r:id="rId170" xr:uid="{00000000-0004-0000-0200-0000A9000000}"/>
+    <hyperlink ref="F29" r:id="rId171" xr:uid="{00000000-0004-0000-0200-0000AA000000}"/>
+    <hyperlink ref="G29" r:id="rId172" xr:uid="{00000000-0004-0000-0200-0000AB000000}"/>
+    <hyperlink ref="I29" r:id="rId173" xr:uid="{00000000-0004-0000-0200-0000AC000000}"/>
+    <hyperlink ref="J29" r:id="rId174" xr:uid="{00000000-0004-0000-0200-0000AD000000}"/>
+    <hyperlink ref="L29" r:id="rId175" xr:uid="{00000000-0004-0000-0200-0000AE000000}"/>
+    <hyperlink ref="M29" r:id="rId176" xr:uid="{00000000-0004-0000-0200-0000AF000000}"/>
+    <hyperlink ref="O29" r:id="rId177" xr:uid="{00000000-0004-0000-0200-0000B0000000}"/>
+    <hyperlink ref="Q29" r:id="rId178" xr:uid="{00000000-0004-0000-0200-0000B1000000}"/>
+    <hyperlink ref="S29" r:id="rId179" xr:uid="{00000000-0004-0000-0200-0000B2000000}"/>
+    <hyperlink ref="C30" r:id="rId180" xr:uid="{00000000-0004-0000-0200-0000B3000000}"/>
+    <hyperlink ref="D30" r:id="rId181" xr:uid="{00000000-0004-0000-0200-0000B4000000}"/>
+    <hyperlink ref="E30" r:id="rId182" xr:uid="{00000000-0004-0000-0200-0000B5000000}"/>
+    <hyperlink ref="F30" r:id="rId183" xr:uid="{00000000-0004-0000-0200-0000B6000000}"/>
+    <hyperlink ref="G30" r:id="rId184" xr:uid="{00000000-0004-0000-0200-0000B7000000}"/>
+    <hyperlink ref="H30" r:id="rId185" xr:uid="{00000000-0004-0000-0200-0000B8000000}"/>
+    <hyperlink ref="I30" r:id="rId186" xr:uid="{00000000-0004-0000-0200-0000B9000000}"/>
+    <hyperlink ref="J30" r:id="rId187" xr:uid="{00000000-0004-0000-0200-0000BA000000}"/>
+    <hyperlink ref="K30" r:id="rId188" xr:uid="{00000000-0004-0000-0200-0000BB000000}"/>
+    <hyperlink ref="L30" r:id="rId189" xr:uid="{00000000-0004-0000-0200-0000BC000000}"/>
+    <hyperlink ref="M30" r:id="rId190" xr:uid="{00000000-0004-0000-0200-0000BD000000}"/>
+    <hyperlink ref="N30" r:id="rId191" xr:uid="{00000000-0004-0000-0200-0000BE000000}"/>
+    <hyperlink ref="O30" r:id="rId192" xr:uid="{00000000-0004-0000-0200-0000BF000000}"/>
+    <hyperlink ref="P30" r:id="rId193" xr:uid="{00000000-0004-0000-0200-0000C0000000}"/>
+    <hyperlink ref="Q30" r:id="rId194" xr:uid="{00000000-0004-0000-0200-0000C1000000}"/>
+    <hyperlink ref="R30" r:id="rId195" xr:uid="{00000000-0004-0000-0200-0000C2000000}"/>
+    <hyperlink ref="S30" r:id="rId196" xr:uid="{00000000-0004-0000-0200-0000C3000000}"/>
+    <hyperlink ref="T30" r:id="rId197" xr:uid="{00000000-0004-0000-0200-0000C4000000}"/>
+    <hyperlink ref="C31" r:id="rId198" xr:uid="{00000000-0004-0000-0200-0000C5000000}"/>
+    <hyperlink ref="D31" r:id="rId199" xr:uid="{00000000-0004-0000-0200-0000C6000000}"/>
+    <hyperlink ref="E31" r:id="rId200" xr:uid="{00000000-0004-0000-0200-0000C7000000}"/>
+    <hyperlink ref="F31" r:id="rId201" xr:uid="{00000000-0004-0000-0200-0000C8000000}"/>
+    <hyperlink ref="L31" r:id="rId202" xr:uid="{00000000-0004-0000-0200-0000C9000000}"/>
+    <hyperlink ref="M31" r:id="rId203" xr:uid="{00000000-0004-0000-0200-0000CA000000}"/>
+    <hyperlink ref="N31" r:id="rId204" xr:uid="{00000000-0004-0000-0200-0000CB000000}"/>
+    <hyperlink ref="P31" r:id="rId205" xr:uid="{00000000-0004-0000-0200-0000CC000000}"/>
+    <hyperlink ref="Q31" r:id="rId206" xr:uid="{00000000-0004-0000-0200-0000CD000000}"/>
+    <hyperlink ref="R31" r:id="rId207" xr:uid="{00000000-0004-0000-0200-0000CE000000}"/>
+    <hyperlink ref="S31" r:id="rId208" xr:uid="{00000000-0004-0000-0200-0000CF000000}"/>
+    <hyperlink ref="T31" r:id="rId209" xr:uid="{00000000-0004-0000-0200-0000D0000000}"/>
+    <hyperlink ref="S32" r:id="rId210" xr:uid="{00000000-0004-0000-0200-0000D1000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
